--- a/multiset_202604/fmo_300k/plot/multiset_64bd_thermo.xlsx
+++ b/multiset_202604/fmo_300k/plot/multiset_64bd_thermo.xlsx
@@ -413,5757 +413,5803 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9.99999999765844e-21</v>
+        <v>9.999999997659603e-21</v>
       </c>
       <c r="B1" t="n">
-        <v>1.000000000015061e-20</v>
+        <v>1.000000000015123e-20</v>
       </c>
       <c r="C1" t="n">
-        <v>9.999999999504483e-21</v>
+        <v>9.999999999505788e-21</v>
       </c>
       <c r="D1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E1" t="n">
-        <v>9.999999997724244e-21</v>
+        <v>9.999999997725314e-21</v>
       </c>
       <c r="F1" t="n">
-        <v>9.999999997803833e-21</v>
+        <v>9.999999997804113e-21</v>
       </c>
       <c r="G1" t="n">
-        <v>9.999999997579826e-21</v>
+        <v>9.999999997581016e-21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.297975533204877e-05</v>
+        <v>5.297628290568715e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>2.601737510550443e-05</v>
+        <v>2.601679447648933e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.953516268167087e-05</v>
+        <v>1.953706460219246e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9947183965882145</v>
+        <v>0.994718125029862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005087331255508085</v>
+        <v>0.005087599702993444</v>
       </c>
       <c r="F2" t="n">
-        <v>1.925939055205755e-05</v>
+        <v>1.926169197476008e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.648047260609948e-05</v>
+        <v>7.648343318577862e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0002100597057891151</v>
+        <v>0.0002100511184263075</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001038470849427296</v>
+        <v>0.000103844870560268</v>
       </c>
       <c r="C3" t="n">
-        <v>8.292265481121995e-05</v>
+        <v>8.292964227111835e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9790642441868834</v>
+        <v>0.9790638993375339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02015491436805903</v>
+        <v>0.02015526110483421</v>
       </c>
       <c r="F3" t="n">
-        <v>7.860658733443323e-05</v>
+        <v>7.860816336348526e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003054054121807317</v>
+        <v>0.0003054057630109988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0004657811717681903</v>
+        <v>0.0004657580974983504</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0002329061056410601</v>
+        <v>0.0002328922987655188</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002039073810453336</v>
+        <v>0.000203915852186605</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9535981304802389</v>
+        <v>0.9535978192329611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04463150650658507</v>
+        <v>0.04463185665676828</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001825876830218294</v>
+        <v>0.0001825811259252674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006851806716995787</v>
+        <v>0.0006851767358954022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008112214541373113</v>
+        <v>0.0008111663704207665</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0004123555182448315</v>
+        <v>0.000412320227117362</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004033662560090127</v>
+        <v>0.000403368339799225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9192180352820677</v>
+        <v>0.9192178865998452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07760418995303256</v>
+        <v>0.07760446867900671</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003381119319489434</v>
+        <v>0.0003380914027532128</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001212719604559648</v>
+        <v>0.001212698381057678</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.001234308626623757</v>
+        <v>0.001234203631296134</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006412760560614971</v>
+        <v>0.0006412199734267323</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0007065724173259157</v>
+        <v>0.000706556969320453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8771079650053213</v>
+        <v>0.8771081840666225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1178734703485318</v>
+        <v>0.1178735046017645</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005535155579253156</v>
+        <v>0.0005534815958619458</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001882891988210538</v>
+        <v>0.001882849161707895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001720273521643675</v>
+        <v>0.001720104349695027</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009188670744814945</v>
+        <v>0.0009187919894289623</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001139926546927441</v>
+        <v>0.001139879470446788</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8286733335372873</v>
+        <v>0.8286739698497403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1640222112696312</v>
+        <v>0.1640219954609924</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000837446456364373</v>
+        <v>0.0008373885080890936</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002687941593664058</v>
+        <v>0.002687870371607092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00225224455730449</v>
+        <v>0.002252006415080154</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001244632252409724</v>
+        <v>0.001244542825229825</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001727629330139188</v>
+        <v>0.001727530121879506</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7754693608563308</v>
+        <v>0.7754703214035525</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2144914686237621</v>
+        <v>0.2144911397445335</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001197645309664535</v>
+        <v>0.001197551209131354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003617019070389262</v>
+        <v>0.003616908280593216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002811994116623747</v>
+        <v>0.002811692082551073</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001618541041483156</v>
+        <v>0.001618433201989189</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00248871968395027</v>
+        <v>0.002488535367737557</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7191278303036696</v>
+        <v>0.7191291834017255</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2676572192775195</v>
+        <v>0.2676567670815233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001639767362060968</v>
+        <v>0.00163962765142573</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004655928214692952</v>
+        <v>0.004655761213047908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00338080048615086</v>
+        <v>0.003380442181105466</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002041093294328469</v>
+        <v>0.002040960726578818</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003434844456808256</v>
+        <v>0.003434539314898683</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6612878791445795</v>
+        <v>0.6612897091105058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3219018137913556</v>
+        <v>0.3219012125328744</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002166388462542576</v>
+        <v>0.002166184122084516</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005787180364234409</v>
+        <v>0.005786952011952707</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.003940397446729275</v>
+        <v>0.003939990891716268</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002513303423394603</v>
+        <v>0.002513130862221117</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004569013808126412</v>
+        <v>0.004568544221222146</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6035334805692718</v>
+        <v>0.6035361880131953</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3756772256962875</v>
+        <v>0.3756761458847112</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002776196999448913</v>
+        <v>0.002775913100390374</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006990382056741543</v>
+        <v>0.006990087026543164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004473934734957935</v>
+        <v>0.004473484191141032</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003036567888209752</v>
+        <v>0.003036343027952344</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005885400477463625</v>
+        <v>0.005884728744818988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.547341075878861</v>
+        <v>0.5473450701233576</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4275565335866479</v>
+        <v>0.4275546154380336</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003463565470854614</v>
+        <v>0.003463188248940763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008242921963005103</v>
+        <v>0.008242570225755539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00496690265949266</v>
+        <v>0.004966418345318206</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003612440619383548</v>
+        <v>0.003612159860051218</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00737016501106762</v>
+        <v>0.007369274241621784</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4940372529464298</v>
+        <v>0.4940426965188759</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4762738767781943</v>
+        <v>0.4762709777526611</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004218423164645521</v>
+        <v>0.004217928246027325</v>
       </c>
       <c r="G13" t="n">
-        <v>0.009520938820786922</v>
+        <v>0.0095205450354442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.005407943427613447</v>
+        <v>0.005407436302600379</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0042423088306618</v>
+        <v>0.004241966899690724</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009003074907417379</v>
+        <v>0.009001972923145082</v>
       </c>
       <c r="D14" t="n">
-        <v>0.444767010455937</v>
+        <v>0.4447737783017666</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5207527342851199</v>
+        <v>0.520748959757956</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005026510530488636</v>
+        <v>0.005025887348879815</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01080041756276205</v>
+        <v>0.01079999846596146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.005789468584757756</v>
+        <v>0.005788954437769857</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004926991591830483</v>
+        <v>0.00492657415855136</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01075967183225136</v>
+        <v>0.01075838180536524</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4004722479973887</v>
+        <v>0.4004798219304994</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5601232899767049</v>
+        <v>0.5601191050698441</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005870019360663287</v>
+        <v>0.005869269541835318</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01205831065640337</v>
+        <v>0.01205789305613518</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.006108063426119078</v>
+        <v>0.006107552999012394</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005666286965935954</v>
+        <v>0.005665792319772277</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01261365232353594</v>
+        <v>0.01261220110284907</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3618787217925847</v>
+        <v>0.3618865021703945</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5937311022446906</v>
+        <v>0.5937270459489618</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006728584932832903</v>
+        <v>0.006727709035664649</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01327358831430117</v>
+        <v>0.01327319642334554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.006364617239189295</v>
+        <v>0.006364110050417059</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006458532047790098</v>
+        <v>0.006457962151340054</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01453920555252512</v>
+        <v>0.01453762169001606</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3294909853061345</v>
+        <v>0.329498518940569</v>
       </c>
       <c r="E17" t="n">
-        <v>0.621138046971949</v>
+        <v>0.6211345084375566</v>
       </c>
       <c r="F17" t="n">
-        <v>0.007580489152234119</v>
+        <v>0.00757950403344034</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01442812373017746</v>
+        <v>0.01442777469666065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.006564184712410557</v>
+        <v>0.00656368000991563</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00730017929748753</v>
+        <v>0.007299533641489945</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01651303567517206</v>
+        <v>0.01651134658915435</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3035942347940972</v>
+        <v>0.3036012608593553</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6421169345171253</v>
+        <v>0.642114106298374</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00840408706736526</v>
+        <v>0.00840302218038187</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01550734393634218</v>
+        <v>0.01550705042132882</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.006715597062886589</v>
+        <v>0.006715101740573056</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008185443661047297</v>
+        <v>0.008184734899173887</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01851588281476231</v>
+        <v>0.01851411788880543</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2842622576158687</v>
+        <v>0.284268662436067</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6566408949406585</v>
+        <v>0.6566388197736349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.009179304512363788</v>
+        <v>0.009178179142170484</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01650061939241256</v>
+        <v>0.0165003841195752</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.006830852845830495</v>
+        <v>0.006830374117684113</v>
       </c>
       <c r="B20" t="n">
-        <v>0.009106105197718902</v>
+        <v>0.00910534267353655</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02053346337331758</v>
+        <v>0.02053166271699015</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2713706624607721</v>
+        <v>0.2713764370991382</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6648684657026712</v>
+        <v>0.6648670738304575</v>
       </c>
       <c r="F20" t="n">
-        <v>0.009889084723547244</v>
+        <v>0.009887913664481822</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01740136569614254</v>
+        <v>0.0174011958977113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.006924333652813273</v>
+        <v>0.006923872685412992</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01005146887734862</v>
+        <v>0.01005065877353035</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02255679431798851</v>
+        <v>0.02255500422067924</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2646147256212533</v>
+        <v>0.2646198189755439</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6671251072255543</v>
+        <v>0.6671243662825918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01052066311236132</v>
+        <v>0.01051946527449405</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01820690719268068</v>
+        <v>0.01820681378774741</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.007011897048557471</v>
+        <v>0.007011454822634677</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01100851504565085</v>
+        <v>0.0110076669627723</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0245819605033874</v>
+        <v>0.02458022910980958</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2635311016133938</v>
+        <v>0.2635354704773455</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6638818506360117</v>
+        <v>0.6638817154658039</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01106655383052447</v>
+        <v>0.01106534445963644</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01891812132247437</v>
+        <v>0.01891811870199724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007109932102342785</v>
+        <v>0.007109506189489008</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01196224921401936</v>
+        <v>0.01196137455577113</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02660942573060197</v>
+        <v>0.02660779665775452</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2675227474805267</v>
+        <v>0.267526413067399</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6557315762173653</v>
+        <v>0.6557319339099322</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01152513101189219</v>
+        <v>0.01152393039977489</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01953893824325157</v>
+        <v>0.01953904521987905</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.007234429051411333</v>
+        <v>0.007234007856487088</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01289624820221176</v>
+        <v>0.01289536325360262</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0286430037753954</v>
+        <v>0.02864150648391902</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2758861499806056</v>
+        <v>0.2758891690153401</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6433636445008744</v>
+        <v>0.6433643575112767</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01190077691850021</v>
+        <v>0.01189961121561128</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02007574757100142</v>
+        <v>0.0200759846637628</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.00740011257919209</v>
+        <v>0.007399678235978374</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0137933772530842</v>
+        <v>0.01379250379472272</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03068862252670471</v>
+        <v>0.03068727917751529</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2878401004968083</v>
+        <v>0.2878425173411575</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6275374640584054</v>
+        <v>0.6275384165294209</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01220356176840641</v>
+        <v>0.01220245876220999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0205367613173989</v>
+        <v>0.02053714615899518</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.007619695887581967</v>
+        <v>0.007619228378496149</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01463662689202285</v>
+        <v>0.01463579434716866</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03275303681570114</v>
+        <v>0.03275186122677485</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3025550828765299</v>
+        <v>0.3025568897100769</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6090556847914654</v>
+        <v>0.6090568199715822</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0124484898614039</v>
+        <v>0.01244747268182801</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02093138287529441</v>
+        <v>0.02093193368407309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.007903291137169371</v>
+        <v>0.00790276708763844</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01541001446943632</v>
+        <v>0.01540925915501249</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03484260347429302</v>
+        <v>0.03484159772793893</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3191824353575349</v>
+        <v>0.3191835434864872</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5887376478711089</v>
+        <v>0.5887390046349031</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01265437884863153</v>
+        <v>0.01265346248426249</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02126962884182591</v>
+        <v>0.02127036542375734</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.008257990181441934</v>
+        <v>0.008257383952395447</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01609948403449037</v>
+        <v>0.0160988474895327</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03696223055337909</v>
+        <v>0.03696137750708949</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3368824549944364</v>
+        <v>0.3368827000036228</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5673937443719062</v>
+        <v>0.56739546270154</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01284247367201853</v>
+        <v>0.01284166479187551</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02156162219232765</v>
+        <v>0.02156256355394419</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.008687628903926756</v>
+        <v>0.0086869132228958</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01669373595884158</v>
+        <v>0.01669325880178313</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03911455049994116</v>
+        <v>0.039113819636665</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3548507061820642</v>
+        <v>0.3548498992300891</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5458012813858644</v>
+        <v>0.5458035513396301</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0130349271342538</v>
+        <v>0.0130342239877865</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0218171699351078</v>
+        <v>0.02181833378115049</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.009192730307951832</v>
+        <v>0.009191879247692962</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01718490606650441</v>
+        <v>0.01718462709946976</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04129938872722411</v>
+        <v>0.04129875175266715</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3723418439204506</v>
+        <v>0.3723398098567908</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5246824100536452</v>
+        <v>0.5246854183997887</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01325328763602652</v>
+        <v>0.01325267927430127</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02204543328819715</v>
+        <v>0.02204683436928957</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.009770620535156191</v>
+        <v>0.009769612052870292</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01756904767147523</v>
+        <v>0.01756900360502708</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04351354945601585</v>
+        <v>0.04351298821443388</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3886902337123871</v>
+        <v>0.3886868636207143</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5046847482561828</v>
+        <v>0.5046886142235752</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01351711472606893</v>
+        <v>0.01351658442273978</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02225468564271398</v>
+        <v>0.02225633386063954</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.01041569790378213</v>
+        <v>0.01041451796502855</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01784637200336701</v>
+        <v>0.01784659626367984</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04575088608320803</v>
+        <v>0.04575039940143071</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4033268164889161</v>
+        <v>0.4033221527903504</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4863652423091502</v>
+        <v>0.4863699210408119</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01384283622799476</v>
+        <v>0.0138423650862954</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02245214898358197</v>
+        <v>0.02245404745240295</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01111982821525356</v>
+        <v>0.01111847172731498</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01802122824197757</v>
+        <v>0.01802175007216432</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04800264496479</v>
+        <v>0.04800224989284675</v>
       </c>
       <c r="D33" t="n">
-        <v>0.415791785940317</v>
+        <v>0.4157860706699755</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4701776908622252</v>
+        <v>0.4701829199887195</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01424292648735005</v>
+        <v>0.01424249607981604</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02264389528808675</v>
+        <v>0.02264604156916307</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.01187283315491565</v>
+        <v>0.0118713012433118</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0181018268899498</v>
+        <v>0.01810267216355205</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05025803449894107</v>
+        <v>0.05025776210912879</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4257427360165183</v>
+        <v>0.4257363858932094</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4564643088131014</v>
+        <v>0.4564696325278427</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01472545251035061</v>
+        <v>0.01472504699652422</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02283480811622299</v>
+        <v>0.02283719906643102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.01266303761529545</v>
+        <v>0.01266133650123586</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01809972709582722</v>
+        <v>0.0181009209477977</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0525049525340241</v>
+        <v>0.05250483868301164</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4329581484200435</v>
+        <v>0.4329517254707924</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4454515504013046</v>
+        <v>0.4454563533103097</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01529399121612872</v>
+        <v>0.01529360015238341</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0230285927173767</v>
+        <v>0.02303122493446931</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.01347784546958041</v>
+        <v>0.01347598686645862</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01802913411292201</v>
+        <v>0.01803070383788534</v>
       </c>
       <c r="C36" t="n">
-        <v>0.05473080021890024</v>
+        <v>0.05473087775158382</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4373362460288057</v>
+        <v>0.4373304367512044</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4372502666807849</v>
+        <v>0.4372538012132701</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0159478816290975</v>
+        <v>0.01594750022053994</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02322782585990915</v>
+        <v>0.02323069335905756</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01430431392811612</v>
+        <v>0.01430231402071106</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0179060655007044</v>
+        <v>0.0179080417565413</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05692331568866701</v>
+        <v>0.05692360766086402</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4388895119616092</v>
+        <v>0.4388850528865731</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4318600068128402</v>
+        <v>0.4318614711801253</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01668274511123362</v>
+        <v>0.0166823747970655</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0234340409968293</v>
+        <v>0.02343713769811969</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.01512969706693058</v>
+        <v>0.01512757190299962</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01774745230433534</v>
+        <v>0.0177498674431728</v>
       </c>
       <c r="C38" t="n">
-        <v>0.05907135097958981</v>
+        <v>0.05907187075807029</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4377352739895535</v>
+        <v>0.4377328533670465</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4291771847536513</v>
+        <v>0.4291758216191375</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01749119906861236</v>
+        <v>0.01749084907823501</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02364784183732724</v>
+        <v>0.02365116583133827</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.01594193110235557</v>
+        <v>0.01593969347214646</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01757024093758157</v>
+        <v>0.01757312516025698</v>
       </c>
       <c r="C39" t="n">
-        <v>0.06116554093138431</v>
+        <v>0.06116629306735127</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4340830265490639</v>
+        <v>0.4340831550498337</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4290065424792346</v>
+        <v>0.4290017705497939</v>
       </c>
       <c r="F39" t="n">
-        <v>0.018363677611688</v>
+        <v>0.01836336640369506</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0238690403886922</v>
+        <v>0.0238725962969225</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.0167300447011779</v>
+        <v>0.0167277039942279</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01739055515445212</v>
+        <v>0.01739393284825076</v>
       </c>
       <c r="C40" t="n">
-        <v>0.06319881418801139</v>
+        <v>0.06319979412100607</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4282191037543314</v>
+        <v>0.4282220425776616</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4310753979501638</v>
+        <v>0.431066884155656</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01928927247385851</v>
+        <v>0.01928903019239977</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02409681177800515</v>
+        <v>0.02410061211079787</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.01748448474575389</v>
+        <v>0.01748204591976238</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01722296999475416</v>
+        <v>0.01722685963645047</v>
       </c>
       <c r="C41" t="n">
-        <v>0.06516671271186288</v>
+        <v>0.06516791231259966</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4204895926048043</v>
+        <v>0.4204953072779236</v>
       </c>
       <c r="E41" t="n">
-        <v>0.435049859144998</v>
+        <v>0.4350375566524267</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02025651868685036</v>
+        <v>0.02025639120806866</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02432986211097651</v>
+        <v>0.02433392699276847</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.01819735208008098</v>
+        <v>0.01819481284233364</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01707993934993969</v>
+        <v>0.017084355620763</v>
       </c>
       <c r="C42" t="n">
-        <v>0.06706751216369362</v>
+        <v>0.0670689270854546</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4112822561286265</v>
+        <v>0.4112904364345563</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4405522688418155</v>
+        <v>0.4405363864691879</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02125407193841278</v>
+        <v>0.02125412375181695</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02456659949743086</v>
+        <v>0.02457095779588766</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.0188625446249254</v>
+        <v>0.01885989372214811</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01697140010366619</v>
+        <v>0.01697635582086894</v>
       </c>
       <c r="C43" t="n">
-        <v>0.06890215114970751</v>
+        <v>0.06890378483628733</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4010082838529699</v>
+        <v>0.4010184169613062</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4471790752264838</v>
+        <v>0.4471599977492589</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02227124122126264</v>
+        <v>0.02227155746334551</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02480530382098467</v>
+        <v>0.02480999344678484</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.01947581246001771</v>
+        <v>0.01947303097783296</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01690456017049365</v>
+        <v>0.01691006699169397</v>
       </c>
       <c r="C44" t="n">
-        <v>0.07067399129117462</v>
+        <v>0.07067585741120619</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3900846298931699</v>
+        <v>0.3900960805335078</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4545183555566483</v>
+        <v>0.4544965602231368</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02329836542159364</v>
+        <v>0.02329905206213256</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02504428520690225</v>
+        <v>0.02504935180048933</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.02003473524323212</v>
+        <v>0.02003179913253909</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01688386127598848</v>
+        <v>0.0168899297137013</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0723884434642225</v>
+        <v>0.07239056806188696</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3789175836346717</v>
+        <v>0.3789296687536934</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4621663119619223</v>
+        <v>0.4621422939340008</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02432704113802671</v>
+        <v>0.02432822157231585</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02528202328193637</v>
+        <v>0.02528751883186222</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.02053863367141816</v>
+        <v>0.02053551559275855</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01691109621754106</v>
+        <v>0.01691773428424605</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07405250490965046</v>
+        <v>0.07405492728200128</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3678881324142753</v>
+        <v>0.3679001816413867</v>
       </c>
       <c r="E46" t="n">
-        <v>0.469742134700983</v>
+        <v>0.4697163524055608</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02535021841173271</v>
+        <v>0.02535202789169003</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0255172796743991</v>
+        <v>0.02552326090235632</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.02098842737737758</v>
+        <v>0.02098509868708341</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0169856527618095</v>
+        <v>0.01699286366565836</v>
       </c>
       <c r="C47" t="n">
-        <v>0.07567425441593402</v>
+        <v>0.07567702394239799</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3573395355312291</v>
+        <v>0.3573509261761345</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4769007593895789</v>
+        <v>0.4768736092617966</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02636219327330053</v>
+        <v>0.02636477425163742</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02574917725077052</v>
+        <v>0.02575570401529177</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.02138645295340537</v>
+        <v>0.0213828860891615</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01710485236033668</v>
+        <v>0.01711263196250272</v>
       </c>
       <c r="C48" t="n">
-        <v>0.07726234808055865</v>
+        <v>0.07726551680720335</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3475673715016204</v>
+        <v>0.3475775379169318</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4833432002679142</v>
+        <v>0.4833150202094066</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02735853148249827</v>
+        <v>0.02736203032288269</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02597724335366655</v>
+        <v>0.02598437669191157</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.02173625435241571</v>
+        <v>0.02173242627607957</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01726435017905166</v>
+        <v>0.01727268469888161</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07882554805324476</v>
+        <v>0.07882916375083444</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3388122161826543</v>
+        <v>0.3388206567253469</v>
       </c>
       <c r="E49" t="n">
-        <v>0.488824260473704</v>
+        <v>0.4887953342513873</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02833595466376041</v>
+        <v>0.0283405182755808</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02620141609516897</v>
+        <v>0.026209216021889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.02204235731960291</v>
+        <v>0.02203825386550031</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0174585638945284</v>
+        <v>0.01746742861124987</v>
       </c>
       <c r="C50" t="n">
-        <v>0.08037231272420692</v>
+        <v>0.08037641463618399</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3312550341075385</v>
+        <v>0.3312613383381507</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4931575032223353</v>
+        <v>0.493128041551582</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02929221320328759</v>
+        <v>0.02929798284756991</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02642201552850037</v>
+        <v>0.02643054014976303</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.02231003891321432</v>
+        <v>0.02230565924537133</v>
       </c>
       <c r="B51" t="n">
-        <v>0.01768110309859973</v>
+        <v>0.01769046280584152</v>
       </c>
       <c r="C51" t="n">
-        <v>0.08191047056725911</v>
+        <v>0.08191508593806815</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3250152553602051</v>
+        <v>0.3250191648719347</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4962174852211726</v>
+        <v>0.496187572569576</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03022596065753144</v>
+        <v>0.03023306186044999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02663968618201798</v>
+        <v>0.02664899270875802</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.02254510072868106</v>
+        <v>0.02254046174595602</v>
       </c>
       <c r="B52" t="n">
-        <v>0.01792517636543924</v>
+        <v>0.01793498834089755</v>
       </c>
       <c r="C52" t="n">
-        <v>0.08344698290243333</v>
+        <v>0.08345212596468782</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3201514081947445</v>
+        <v>0.3201528879951566</v>
       </c>
       <c r="E52" t="n">
-        <v>0.49793937413527</v>
+        <v>0.497908901908793</v>
       </c>
       <c r="F52" t="n">
-        <v>0.03113663831798106</v>
+        <v>0.03114516822829757</v>
       </c>
       <c r="G52" t="n">
-        <v>0.02685531935545096</v>
+        <v>0.02686546581621124</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.02275365233331465</v>
+        <v>0.02274879258995607</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0181839588932616</v>
+        <v>0.01819417902202839</v>
       </c>
       <c r="C53" t="n">
-        <v>0.08498779099934944</v>
+        <v>0.08499346994879704</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3166641020358972</v>
+        <v>0.3166633892429845</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4983161584565994</v>
+        <v>0.4982847723704147</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03202437349491769</v>
+        <v>0.0320343871212278</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02706996378666028</v>
+        <v>0.02708100970459166</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.02294191002763344</v>
+        <v>0.02293689246726194</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01845090975024484</v>
+        <v>0.01846150147020631</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08653774494476889</v>
+        <v>0.08654397536913537</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3145010789957659</v>
+        <v>0.3144987022503964</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4973937357377317</v>
+        <v>0.4973608044675561</v>
       </c>
       <c r="F54" t="n">
-        <v>0.03288988748184071</v>
+        <v>0.03290138561045829</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0272847330620145</v>
+        <v>0.02729673836498556</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.02311601467347047</v>
+        <v>0.02311092783413967</v>
       </c>
       <c r="B55" t="n">
-        <v>0.01872003246790876</v>
+        <v>0.01873097733215011</v>
       </c>
       <c r="C55" t="n">
-        <v>0.08810060526297041</v>
+        <v>0.08810742424605636</v>
       </c>
       <c r="D55" t="n">
-        <v>0.313563981662098</v>
+        <v>0.313560753836959</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4952642418814646</v>
+        <v>0.4952288479701777</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03373440624787782</v>
+        <v>0.03374732883739599</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0275007178042101</v>
+        <v>0.02751373994312119</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.02328187106086083</v>
+        <v>0.02327682870222854</v>
       </c>
       <c r="B56" t="n">
-        <v>0.01898607666122141</v>
+        <v>0.01899738493965784</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0896790957982683</v>
+        <v>0.08968657700184895</v>
       </c>
       <c r="D56" t="n">
-        <v>0.313716427090075</v>
+        <v>0.3137134142554238</v>
       </c>
       <c r="E56" t="n">
-        <v>0.492058049791229</v>
+        <v>0.4920190004145189</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03455956955326085</v>
+        <v>0.03457379544899466</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02771891004508451</v>
+        <v>0.02773299923732701</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.02344501057260522</v>
+        <v>0.02344014918072198</v>
       </c>
       <c r="B57" t="n">
-        <v>0.01924468163300551</v>
+        <v>0.01925640109605531</v>
       </c>
       <c r="C57" t="n">
-        <v>0.09127498965107513</v>
+        <v>0.09128326020974752</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3147929380193358</v>
+        <v>0.3147914162050249</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4879349014217931</v>
+        <v>0.4878907494988366</v>
       </c>
       <c r="F57" t="n">
-        <v>0.03536733420979971</v>
+        <v>0.0353826860207633</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02794014449238574</v>
+        <v>0.02795533778885039</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.02361047747890064</v>
+        <v>0.02360595138697735</v>
       </c>
       <c r="B58" t="n">
-        <v>0.01949246496267458</v>
+        <v>0.01950468608954514</v>
       </c>
       <c r="C58" t="n">
-        <v>0.09288921780177188</v>
+        <v>0.09289847208567939</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3166082864446805</v>
+        <v>0.3166096765194583</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4830746271941244</v>
+        <v>0.4830237192394716</v>
       </c>
       <c r="F58" t="n">
-        <v>0.03615986770272635</v>
+        <v>0.03617612086553249</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0281650584151216</v>
+        <v>0.02818137381333569</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.0237827384282533</v>
+        <v>0.02377871357313562</v>
       </c>
       <c r="B59" t="n">
-        <v>0.01972706017699385</v>
+        <v>0.01973991667552196</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09452198688579393</v>
+        <v>0.09453249110753149</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3189668304117368</v>
+        <v>0.3189725819539361</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4776678819098509</v>
+        <v>0.4776084674813659</v>
       </c>
       <c r="F59" t="n">
-        <v>0.03693943218778947</v>
+        <v>0.03695632752723443</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02839406999958151</v>
+        <v>0.02841150168127453</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.02396561487318769</v>
+        <v>0.02396226263388892</v>
       </c>
       <c r="B60" t="n">
-        <v>0.01994710867646133</v>
+        <v>0.01996077285559263</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09617289093349239</v>
+        <v>0.09618497612357441</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3216714442168397</v>
+        <v>0.3216828636872737</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4719073048259079</v>
+        <v>0.4718377141620176</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03770826268155089</v>
+        <v>0.037725521497549</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02862737379256014</v>
+        <v>0.02864588904010362</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.02416223826664296</v>
+        <v>0.02415973023847341</v>
       </c>
       <c r="B61" t="n">
-        <v>0.02015221161701762</v>
+        <v>0.02016688487235557</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09784100721599086</v>
+        <v>0.09785505132211277</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3245316732559415</v>
+        <v>0.3245497192396266</v>
       </c>
       <c r="E61" t="n">
-        <v>0.465979473617955</v>
+        <v>0.4658983399006436</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03846844561724957</v>
+        <v>0.03848578594229268</v>
       </c>
       <c r="G61" t="n">
-        <v>0.02886495040920254</v>
+        <v>0.02888448848449502</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.02437502758395262</v>
+        <v>0.02437353147561099</v>
       </c>
       <c r="B62" t="n">
-        <v>0.02034284755339974</v>
+        <v>0.02035874688522375</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09952497407412045</v>
+        <v>0.09954137430787027</v>
       </c>
       <c r="D62" t="n">
-        <v>0.327370799100624</v>
+        <v>0.3273958826618726</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4600579599332742</v>
+        <v>0.4599644465221021</v>
       </c>
       <c r="F62" t="n">
-        <v>0.03922180514548684</v>
+        <v>0.0392389581709594</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02910658660914228</v>
+        <v>0.02912705997636083</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.02460568842328476</v>
+        <v>0.02460536473395236</v>
       </c>
       <c r="B63" t="n">
-        <v>0.02052026182529192</v>
+        <v>0.02053760376342292</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1012230510408099</v>
+        <v>0.1012421885573107</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3300315915738016</v>
+        <v>0.3300634183309416</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4542976998894374</v>
+        <v>0.4541916931636172</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03996980537732302</v>
+        <v>0.03998653139947335</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02935190187005124</v>
+        <v>0.02937320005128218</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.02485523233383296</v>
+        <v>0.02485623143171999</v>
       </c>
       <c r="B64" t="n">
-        <v>0.02068633400949628</v>
+        <v>0.02070531735744445</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1029331612777704</v>
+        <v>0.1029553625731327</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3323806292891556</v>
+        <v>0.3324181026092175</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4488307884353788</v>
+        <v>0.4487130319035932</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04071347642642518</v>
+        <v>0.04072957959272731</v>
       </c>
       <c r="G64" t="n">
-        <v>0.02960037822794085</v>
+        <v>0.029622374532165</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.02512401454087122</v>
+        <v>0.02512647382427764</v>
       </c>
       <c r="B65" t="n">
-        <v>0.02084343009394253</v>
+        <v>0.02086421861900224</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1046529183371544</v>
+        <v>0.1046784192169839</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3343111516769649</v>
+        <v>0.3343523436042349</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4437637244852023</v>
+        <v>0.4436358809074707</v>
       </c>
       <c r="F65" t="n">
-        <v>0.04145337009445936</v>
+        <v>0.04146871161660897</v>
       </c>
       <c r="G65" t="n">
-        <v>0.02985139077140513</v>
+        <v>0.02987395221142185</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.02541178788230249</v>
+        <v>0.02541582864185965</v>
       </c>
       <c r="B66" t="n">
-        <v>0.02099424625763108</v>
+        <v>0.02101695231533121</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1063796437557771</v>
+        <v>0.1064085612051882</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3357444704842064</v>
+        <v>0.3357866635371801</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4391760662275292</v>
+        <v>0.4390406985835418</v>
       </c>
       <c r="F66" t="n">
-        <v>0.04218954854554248</v>
+        <v>0.04220405853553871</v>
       </c>
       <c r="G66" t="n">
-        <v>0.03010423684701083</v>
+        <v>0.03012723718136024</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.02571777051944969</v>
+        <v>0.02572349414871791</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0211416511503051</v>
+        <v>0.02116632135525897</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1081103858610617</v>
+        <v>0.108142700669647</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3366300374334549</v>
+        <v>0.3366698334239842</v>
       </c>
       <c r="E67" t="n">
-        <v>0.435120385214039</v>
+        <v>0.434980857831948</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04292160688195909</v>
+        <v>0.04293529457956561</v>
       </c>
       <c r="G67" t="n">
-        <v>0.03035816293973004</v>
+        <v>0.03038149799087853</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.02604072462580297</v>
+        <v>0.02604820813149821</v>
       </c>
       <c r="B68" t="n">
-        <v>0.02128853333895875</v>
+        <v>0.02131513766433256</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1098419495421978</v>
+        <v>0.1098775000329059</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3369443274940861</v>
+        <v>0.3369778097685722</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4316233484646621</v>
+        <v>0.4314836627111605</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0436487275875387</v>
+        <v>0.04366168902347197</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0306123889467539</v>
+        <v>0.03063599266805875</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.02637904282205508</v>
+        <v>0.02638833404803113</v>
       </c>
       <c r="B69" t="n">
-        <v>0.02143766025056671</v>
+        <v>0.02146608609910868</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1115709428099798</v>
+        <v>0.1116094284064118</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3366887450926473</v>
+        <v>0.3367116750222747</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4286877173409719</v>
+        <v>0.4285523035657239</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04436976171521194</v>
+        <v>0.04438218353975786</v>
       </c>
       <c r="G69" t="n">
-        <v>0.03086612996856704</v>
+        <v>0.03088998931869199</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.02673083883076753</v>
+        <v>0.02674195216491367</v>
       </c>
       <c r="B70" t="n">
-        <v>0.02159155447370768</v>
+        <v>0.02162160694060369</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1132938417988143</v>
+        <v>0.1133348335459851</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3358867869228305</v>
+        <v>0.3358948137000317</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4262950328238025</v>
+        <v>0.4261685234506228</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0450833292325431</v>
+        <v>0.04509548775634182</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03111861591753453</v>
+        <v>0.03114278244150131</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.02709403874360751</v>
+        <v>0.02710695220504965</v>
       </c>
       <c r="B71" t="n">
-        <v>0.02175239239521108</v>
+        <v>0.02178380134090382</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1150070713213133</v>
+        <v>0.1150500259036454</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3345806806715573</v>
+        <v>0.3345695494699091</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4244087784924896</v>
+        <v>0.4242957810066307</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04578792938924173</v>
+        <v>0.04580018474317412</v>
       </c>
       <c r="G71" t="n">
-        <v>0.03136910898657976</v>
+        <v>0.03139370533068714</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.02746646957566514</v>
+        <v>0.02748112399235026</v>
       </c>
       <c r="B72" t="n">
-        <v>0.02192192910799341</v>
+        <v>0.02195436296054016</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1167070953801547</v>
+        <v>0.1167513693555609</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3328276784640913</v>
+        <v>0.3327934374911545</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4229778570968029</v>
+        <v>0.4228827294276394</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04648205149103781</v>
+        <v>0.04649483773452009</v>
       </c>
       <c r="G72" t="n">
-        <v>0.03161691888425477</v>
+        <v>0.03164213903823443</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.02784594217013094</v>
+        <v>0.02786224282709332</v>
       </c>
       <c r="B73" t="n">
-        <v>0.02210145176042285</v>
+        <v>0.02213453740938938</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1183905101724645</v>
+        <v>0.1184353723714348</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3306961615235771</v>
+        <v>0.3306353836892658</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4219402416505</v>
+        <v>0.4218668554334658</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04716427730269495</v>
+        <v>0.04717808980397328</v>
       </c>
       <c r="G73" t="n">
-        <v>0.03186141542020976</v>
+        <v>0.03188751846537785</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.02823032596022888</v>
+        <v>0.02824814669797598</v>
       </c>
       <c r="B74" t="n">
-        <v>0.02229176156186312</v>
+        <v>0.02232510900197642</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1200541318345983</v>
+        <v>0.1200987732451042</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3282617301443131</v>
+        <v>0.3281717520611241</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4212266442072492</v>
+        <v>0.4211781335856722</v>
       </c>
       <c r="F74" t="n">
-        <v>0.04783336832335379</v>
+        <v>0.04784874941541526</v>
       </c>
       <c r="G74" t="n">
-        <v>0.03210203796839327</v>
+        <v>0.03212933599273207</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.02861761351896952</v>
+        <v>0.02863680288526737</v>
       </c>
       <c r="B75" t="n">
-        <v>0.02249318273428904</v>
+        <v>0.02252641241679712</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1216950717118355</v>
+        <v>0.1217386135192295</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3256034420380499</v>
+        <v>0.3254825932086521</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4207640552736572</v>
+        <v>0.4207425787171897</v>
       </c>
       <c r="F75" t="n">
-        <v>0.04848833361395142</v>
+        <v>0.04850585662949439</v>
       </c>
       <c r="G75" t="n">
-        <v>0.03233830110924725</v>
+        <v>0.03236714262336989</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.02900597337402699</v>
+        <v>0.02902636209806387</v>
       </c>
       <c r="B76" t="n">
-        <v>0.02270559524145402</v>
+        <v>0.02273836534048148</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1233107939865202</v>
+        <v>0.1233522950021668</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3228002980014258</v>
+        <v>0.3226480834481733</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4204790677410336</v>
+        <v>0.4204856202737607</v>
       </c>
       <c r="F76" t="n">
-        <v>0.04912847566788494</v>
+        <v>0.0491487273239425</v>
       </c>
       <c r="G76" t="n">
-        <v>0.03256979598765463</v>
+        <v>0.03260054651341084</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.02939379015689442</v>
+        <v>0.02941519896988383</v>
       </c>
       <c r="B77" t="n">
-        <v>0.02292848694475107</v>
+        <v>0.02296051711110013</v>
       </c>
       <c r="C77" t="n">
-        <v>0.124899153354529</v>
+        <v>0.1249376176875912</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3199280263206989</v>
+        <v>0.3197452396533621</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4203009422786768</v>
+        <v>0.4203352417959293</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04975341350185405</v>
+        <v>0.04977697552496794</v>
       </c>
       <c r="G77" t="n">
-        <v>0.03279618744259589</v>
+        <v>0.03282920925716547</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.02977969170849018</v>
+        <v>0.02980193837451243</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02316101993167449</v>
+        <v>0.02319210799542213</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1264584123892404</v>
+        <v>0.1264927980823113</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3170562127220894</v>
+        <v>0.3168449811487865</v>
       </c>
       <c r="E78" t="n">
-        <v>0.42016437172642</v>
+        <v>0.420224817688974</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0503630840350295</v>
+        <v>0.05039051592154165</v>
       </c>
       <c r="G78" t="n">
-        <v>0.03301720748705579</v>
+        <v>0.03305284078845148</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.03016256310376612</v>
+        <v>0.03018546759769416</v>
       </c>
       <c r="B79" t="n">
-        <v>0.02340210510360681</v>
+        <v>0.02343213420373254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1279872401691977</v>
+        <v>0.128016469486246</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3142458505924647</v>
+        <v>0.31400962279334</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4200118706244488</v>
+        <v>0.4200955626588357</v>
       </c>
       <c r="F79" t="n">
-        <v>0.05095772447828818</v>
+        <v>0.05098954954262532</v>
       </c>
       <c r="G79" t="n">
-        <v>0.03323264592822765</v>
+        <v>0.03327119371752642</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.03054154829111792</v>
+        <v>0.0305649350463013</v>
       </c>
       <c r="B80" t="n">
-        <v>0.02365047932057517</v>
+        <v>0.0236794147512032</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1294846944256922</v>
+        <v>0.1295076673924212</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3115474109551627</v>
+        <v>0.3112908836899668</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4197956880763779</v>
+        <v>0.4198985057220759</v>
       </c>
       <c r="F80" t="n">
-        <v>0.05153783970406733</v>
+        <v>0.05157453584887095</v>
       </c>
       <c r="G80" t="n">
-        <v>0.03344233922700698</v>
+        <v>0.03348405754916072</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.03091604051663477</v>
+        <v>0.03093973697584045</v>
       </c>
       <c r="B81" t="n">
-        <v>0.02390478011833085</v>
+        <v>0.02393265726509747</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1309501905081304</v>
+        <v>0.1309658041947686</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3089995407117747</v>
+        <v>0.3087284884737559</v>
       </c>
       <c r="E81" t="n">
-        <v>0.4194791304757646</v>
+        <v>0.4195959055356709</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05210415885144246</v>
+        <v>0.0521461545962209</v>
       </c>
       <c r="G81" t="n">
-        <v>0.03364615881792251</v>
+        <v>0.03369125295864578</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.03128566319349101</v>
+        <v>0.0313094944725626</v>
       </c>
       <c r="B82" t="n">
-        <v>0.02416361421103864</v>
+        <v>0.02419052047555374</v>
       </c>
       <c r="C82" t="n">
-        <v>0.132383461515399</v>
+        <v>0.1323906373507469</v>
       </c>
       <c r="D82" t="n">
-        <v>0.306628495415791</v>
+        <v>0.3063494419236852</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4190371802744744</v>
+        <v>0.4191620186856309</v>
       </c>
       <c r="F82" t="n">
-        <v>0.05265758530208833</v>
+        <v>0.0527052608203066</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03384400008771743</v>
+        <v>0.03389262627151397</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.03165024323584155</v>
+        <v>0.03167402337301163</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0244256172050166</v>
+        <v>0.02445167148689165</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1337845131136529</v>
+        <v>0.1337822333586098</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3044483805055431</v>
+        <v>0.3041680816320759</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4184563292659039</v>
+        <v>0.4185831098646327</v>
       </c>
       <c r="F83" t="n">
-        <v>0.05319914368160999</v>
+        <v>0.05325283591301866</v>
       </c>
       <c r="G83" t="n">
-        <v>0.03403577299243203</v>
+        <v>0.03408804437176009</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.03200977888851814</v>
+        <v>0.03203329988489168</v>
       </c>
       <c r="B84" t="n">
-        <v>0.02468950300687284</v>
+        <v>0.02471483617050547</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1351535774244267</v>
+        <v>0.1351409268854468</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3024622012665839</v>
+        <v>0.3021870140343981</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4177336175198302</v>
+        <v>0.4178565956317838</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0537299271097566</v>
+        <v>0.05378993714965922</v>
       </c>
       <c r="G84" t="n">
-        <v>0.03422139478401182</v>
+        <v>0.03427739024331515</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.03236440421940067</v>
+        <v>0.03238742456121775</v>
       </c>
       <c r="B85" t="n">
-        <v>0.02495410228469981</v>
+        <v>0.02497884127725373</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1364910665069576</v>
+        <v>0.1364672732234991</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3006636329560549</v>
+        <v>0.3003989324851092</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4168749618861559</v>
+        <v>0.4169893215869623</v>
       </c>
       <c r="F85" t="n">
-        <v>0.05425104712568131</v>
+        <v>0.05431764769051906</v>
       </c>
       <c r="G85" t="n">
-        <v>0.03440078502104968</v>
+        <v>0.03446055917543863</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.03271435233028964</v>
+        <v>0.03273658712157008</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02521838997313135</v>
+        <v>0.02524264723200552</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1377975277964083</v>
+        <v>0.1377619948597098</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2990393527431596</v>
+        <v>0.2987891162830479</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4158929263748781</v>
+        <v>0.4159951698816884</v>
       </c>
       <c r="F86" t="n">
-        <v>0.05476358828563221</v>
+        <v>0.05483702914081037</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0345738624965006</v>
+        <v>0.03463745548116769</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.03305991984535344</v>
+        <v>0.03308103434878847</v>
       </c>
       <c r="B87" t="n">
-        <v>0.02548150230795816</v>
+        <v>0.02550537104761702</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1390735987096214</v>
+        <v>0.1390259260482076</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2975717074435921</v>
+        <v>0.2973382676096261</v>
       </c>
       <c r="E87" t="n">
-        <v>0.414804158514672</v>
+        <v>0.41489233272206</v>
       </c>
       <c r="F87" t="n">
-        <v>0.05526856936286816</v>
+        <v>0.05534907868226304</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0347405438159349</v>
+        <v>0.03480798954143772</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.03340143439796268</v>
+        <v>0.03342104282499933</v>
       </c>
       <c r="B88" t="n">
-        <v>0.02574274452339543</v>
+        <v>0.02576629935701902</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1403199640064703</v>
+        <v>0.1402599596609005</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2962414145889229</v>
+        <v>0.2960253321652628</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4136267880277908</v>
+        <v>0.4137005985954984</v>
       </c>
       <c r="F88" t="n">
-        <v>0.05576691136608539</v>
+        <v>0.05585469232422915</v>
       </c>
       <c r="G88" t="n">
-        <v>0.03490074308937249</v>
+        <v>0.03497207507209098</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.03373922695090278</v>
+        <v>0.03375689767077797</v>
       </c>
       <c r="B89" t="n">
-        <v>0.02600159014279413</v>
+        <v>0.02602489214090777</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1415373165592733</v>
+        <v>0.1414649995037872</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2950299641734274</v>
+        <v>0.2948300017844904</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4123781159642525</v>
+        <v>0.4124389468590572</v>
       </c>
       <c r="F89" t="n">
-        <v>0.05625941366382384</v>
+        <v>0.05635463537621255</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03505437254552594</v>
+        <v>0.03512962666476691</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.03407361006440965</v>
+        <v>0.03408887776296718</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0262576736204675</v>
+        <v>0.0262807781651992</v>
       </c>
       <c r="C90" t="n">
-        <v>0.1427263235028243</v>
+        <v>0.1426419205340728</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2939214752000243</v>
+        <v>0.2937346754740887</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4110728358080875</v>
+        <v>0.4111236691220188</v>
       </c>
       <c r="F90" t="n">
-        <v>0.05674673775695956</v>
+        <v>0.05684952109476062</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0352013440472273</v>
+        <v>0.03528055784689266</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.03440486264296502</v>
+        <v>0.03441724715532424</v>
       </c>
       <c r="B91" t="n">
-        <v>0.02651077705023028</v>
+        <v>0.02653374333348567</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1438875994215031</v>
+        <v>0.1437915388392113</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2929039035571601</v>
+        <v>0.2927257631926335</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4097218858916154</v>
+        <v>0.4097671290163972</v>
       </c>
       <c r="F91" t="n">
-        <v>0.05722939956786638</v>
+        <v>0.05733979838111293</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03534157186865946</v>
+        <v>0.03542478008183519</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.03473322097076754</v>
+        <v>0.03474225174461433</v>
       </c>
       <c r="B92" t="n">
-        <v>0.02676081252417125</v>
+        <v>0.02678371318062435</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1450216872102132</v>
+        <v>0.1449145922400201</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2919696150560201</v>
+        <v>0.2917943243438429</v>
       </c>
       <c r="E92" t="n">
-        <v>0.4083319188457587</v>
+        <v>0.4083771661228358</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05770776922658467</v>
+        <v>0.0578257491778123</v>
       </c>
       <c r="G92" t="n">
-        <v>0.03547497616648474</v>
+        <v>0.03556220319025023</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.03505887532090458</v>
+        <v>0.03506411975485218</v>
       </c>
       <c r="B93" t="n">
-        <v>0.02700780071062773</v>
+        <v>0.02703073070974223</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1461290504416334</v>
+        <v>0.1460117309477396</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2911153834314338</v>
+        <v>0.2909361075119332</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4069053240792951</v>
+        <v>0.4069570776824249</v>
       </c>
       <c r="F93" t="n">
-        <v>0.05818207834258093</v>
+        <v>0.05830749583551276</v>
       </c>
       <c r="G93" t="n">
-        <v>0.03560148767352454</v>
+        <v>0.03569273755779508</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.03538197143913256</v>
+        <v>0.03538306436801932</v>
       </c>
       <c r="B94" t="n">
-        <v>0.02725184644419426</v>
+        <v>0.02727493078021787</v>
       </c>
       <c r="C94" t="n">
-        <v>0.147210074127654</v>
+        <v>0.1470835162057886</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2903419236653624</v>
+        <v>0.2901511056099112</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4054406966519308</v>
+        <v>0.4055060665295154</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05865243469765655</v>
+        <v>0.05878501822382787</v>
       </c>
       <c r="G94" t="n">
-        <v>0.03572105297406892</v>
+        <v>0.03581629828271966</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.03570261544332927</v>
+        <v>0.03569928680779365</v>
       </c>
       <c r="B95" t="n">
-        <v>0.02749311177046142</v>
+        <v>0.0275165122869655</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1482650710405718</v>
+        <v>0.1481304237263427</v>
       </c>
       <c r="D95" t="n">
-        <v>0.289653106118776</v>
+        <v>0.2894427748965041</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4039336108064869</v>
+        <v>0.4040200113591808</v>
       </c>
       <c r="F95" t="n">
-        <v>0.05911884402664552</v>
+        <v>0.05925817973801324</v>
       </c>
       <c r="G95" t="n">
-        <v>0.03583364079372892</v>
+        <v>0.03593281118520036</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.03602088067151073</v>
+        <v>0.03601297838824959</v>
       </c>
       <c r="B96" t="n">
-        <v>0.02773178809275607</v>
+        <v>0.02775570941304457</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1492942909219469</v>
+        <v>0.1491528484800719</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2890550134026715</v>
+        <v>0.2888170781485899</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4023775399937969</v>
+        <v>0.4024924045488764</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05958123819016353</v>
+        <v>0.05972676062735569</v>
       </c>
       <c r="G96" t="n">
-        <v>0.03593924872715412</v>
+        <v>0.0360422203938121</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.03633681470526737</v>
+        <v>0.03632432045772475</v>
       </c>
       <c r="B97" t="n">
-        <v>0.02796806830273679</v>
+        <v>0.02799276326804117</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1502979272730105</v>
+        <v>0.1501511083311112</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2885549572037057</v>
+        <v>0.2882814888971279</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4007648137361958</v>
+        <v>0.4009153255831431</v>
       </c>
       <c r="F97" t="n">
-        <v>0.06003950795923204</v>
+        <v>0.06019049641548611</v>
       </c>
       <c r="G97" t="n">
-        <v>0.03603791081985184</v>
+        <v>0.03614449704736569</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.03665044535297909</v>
+        <v>0.03663348171369627</v>
       </c>
       <c r="B98" t="n">
-        <v>0.02820212054603596</v>
+        <v>0.02822789522809522</v>
       </c>
       <c r="C98" t="n">
-        <v>0.151276120683527</v>
+        <v>0.1511254459127979</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2881605191702242</v>
+        <v>0.2878440435501559</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3990875502762907</v>
+        <v>0.3992803663119783</v>
       </c>
       <c r="F98" t="n">
-        <v>0.06049353915293079</v>
+        <v>0.06064911876802116</v>
       </c>
       <c r="G98" t="n">
-        <v>0.03612970481801227</v>
+        <v>0.03623964851525486</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.03696178462012058</v>
+        <v>0.03694061290824532</v>
       </c>
       <c r="B99" t="n">
-        <v>0.02843406530113555</v>
+        <v>0.02846128325604026</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1522289605552119</v>
+        <v>0.1520760300337</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2878786463916707</v>
+        <v>0.2875124772268193</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3973385348449044</v>
+        <v>0.3975794731036608</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06094324908913934</v>
+        <v>0.06110239601766729</v>
       </c>
       <c r="G99" t="n">
-        <v>0.03621475919781758</v>
+        <v>0.03632772745386678</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.03727082999433211</v>
+        <v>0.03724583940223361</v>
       </c>
       <c r="B100" t="n">
-        <v>0.02866395694845571</v>
+        <v>0.02869304239717138</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1531564885579443</v>
+        <v>0.1530029587488404</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2877148234146341</v>
+        <v>0.287293447670475</v>
       </c>
       <c r="E100" t="n">
-        <v>0.3955120212450458</v>
+        <v>0.3958057011708871</v>
       </c>
       <c r="F100" t="n">
-        <v>0.06138862110018711</v>
+        <v>0.06155017060268456</v>
       </c>
       <c r="G100" t="n">
-        <v>0.03629325873940054</v>
+        <v>0.03640884000770785</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.03757756345465895</v>
+        <v>0.03754925232577043</v>
       </c>
       <c r="B101" t="n">
-        <v>0.02889177146508672</v>
+        <v>0.02892321049345998</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1540587052307753</v>
+        <v>0.153906265847396</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2876723529799446</v>
+        <v>0.2871918410566128</v>
       </c>
       <c r="E101" t="n">
-        <v>0.3936044241948425</v>
+        <v>0.3939538869074226</v>
       </c>
       <c r="F101" t="n">
-        <v>0.06182973327350263</v>
+        <v>0.06199239083527144</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03636544940118928</v>
+        <v>0.03648315253406713</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.03788194819988127</v>
+        <v>0.03785089927174101</v>
       </c>
       <c r="B102" t="n">
-        <v>0.02911740043952522</v>
+        <v>0.02915173990673072</v>
       </c>
       <c r="C102" t="n">
-        <v>0.154935581706092</v>
+        <v>0.1547859315849698</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2877517761654235</v>
+        <v>0.2872101536516498</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3916148740483674</v>
+        <v>0.3920212445228443</v>
       </c>
       <c r="F102" t="n">
-        <v>0.06226677895426953</v>
+        <v>0.06242913470430334</v>
       </c>
       <c r="G102" t="n">
-        <v>0.03643164048644123</v>
+        <v>0.0365508963577611</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.03818392403200738</v>
+        <v>0.03815077550870676</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0293406522476387</v>
+        <v>0.02937849567489375</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1557870769181663</v>
+        <v>0.1556418976970982</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2879504565009847</v>
+        <v>0.2873479467448335</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3895456095146133</v>
+        <v>0.3900078902896822</v>
       </c>
       <c r="F103" t="n">
-        <v>0.06270007609000378</v>
+        <v>0.06286062387764722</v>
       </c>
       <c r="G103" t="n">
-        <v>0.03649220469658638</v>
+        <v>0.03661237020713865</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.03848340233168594</v>
+        <v>0.03844881667092052</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0295612597962131</v>
+        <v>0.02960326007417068</v>
       </c>
       <c r="C104" t="n">
-        <v>0.156613157577832</v>
+        <v>0.156474086243291</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2882623345282142</v>
+        <v>0.2876013785835286</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3874022061209382</v>
+        <v>0.3879172915756041</v>
       </c>
       <c r="F104" t="n">
-        <v>0.06313006457424973</v>
+        <v>0.06328722672594508</v>
       </c>
       <c r="G104" t="n">
-        <v>0.03654757507086685</v>
+        <v>0.03666794012653983</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.03878026135239538</v>
+        <v>0.03874489377859758</v>
       </c>
       <c r="B105" t="n">
-        <v>0.02977889436638619</v>
+        <v>0.02982574307786889</v>
       </c>
       <c r="C105" t="n">
-        <v>0.157413821394073</v>
+        <v>0.1572824215074387</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2886778380747212</v>
+        <v>0.2879628287173736</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3851936553782279</v>
+        <v>0.385756626126283</v>
       </c>
       <c r="F105" t="n">
-        <v>0.06355729055146001</v>
+        <v>0.06370944999896574</v>
       </c>
       <c r="G105" t="n">
-        <v>0.03659823888273635</v>
+        <v>0.03671803679347241</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.03907434307361369</v>
+        <v>0.0390388112609045</v>
       </c>
       <c r="B106" t="n">
-        <v>0.02999318447076867</v>
+        <v>0.03004559775087213</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1581891217558643</v>
+        <v>0.158066853900319</v>
       </c>
       <c r="D106" t="n">
-        <v>0.2891839171265344</v>
+        <v>0.288420647762623</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3829323251935172</v>
+        <v>0.3835370193778982</v>
       </c>
       <c r="F106" t="n">
-        <v>0.06398237951124341</v>
+        <v>0.06412791966045374</v>
       </c>
       <c r="G106" t="n">
-        <v>0.03664472886845831</v>
+        <v>0.03676315028692932</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.0393654515332752</v>
+        <v>0.03933030839970695</v>
       </c>
       <c r="B107" t="n">
-        <v>0.03020373784569303</v>
+        <v>0.03026243926911728</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1589391912315587</v>
+        <v>0.1588273844555088</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2897641664243277</v>
+        <v>0.2889590832060498</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3806338415152888</v>
+        <v>0.3812736100084634</v>
       </c>
       <c r="F107" t="n">
-        <v>0.06440599959536829</v>
+        <v>0.06454335220150054</v>
       </c>
       <c r="G107" t="n">
-        <v>0.03668761185448805</v>
+        <v>0.03680382245965338</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.0396533537802161</v>
+        <v>0.03961906430788785</v>
       </c>
       <c r="B108" t="n">
-        <v>0.03041016545467861</v>
+        <v>0.0304758660522315</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1596642630287605</v>
+        <v>0.1595640880439329</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2903990137356598</v>
+        <v>0.289558437505695</v>
       </c>
       <c r="E108" t="n">
-        <v>0.3783169091079466</v>
+        <v>0.3789853885070682</v>
       </c>
       <c r="F108" t="n">
-        <v>0.06482881884392358</v>
+        <v>0.06495651841084693</v>
       </c>
       <c r="G108" t="n">
-        <v>0.03672747604881445</v>
+        <v>0.03684063717233729</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.03993778287229365</v>
+        <v>0.0399047062469542</v>
       </c>
       <c r="B109" t="n">
-        <v>0.03061210528721096</v>
+        <v>0.03068548145711008</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1603646874731663</v>
+        <v>0.160277132974446</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2910659822378739</v>
+        <v>0.290195498924658</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3760030655448354</v>
+        <v>0.3766947696124453</v>
       </c>
       <c r="F109" t="n">
-        <v>0.06525145926726381</v>
+        <v>0.06536820203478183</v>
       </c>
       <c r="G109" t="n">
-        <v>0.03676491731735582</v>
+        <v>0.03687420874960431</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.04021844309719284</v>
+        <v>0.04018682081109076</v>
       </c>
       <c r="B110" t="n">
-        <v>0.03080924454763736</v>
+        <v>0.03089091457720949</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1610409424064912</v>
+        <v>0.1609667946127499</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2917400694468038</v>
+        <v>0.2908442501707207</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3737163232576943</v>
+        <v>0.3744268946956533</v>
       </c>
       <c r="F110" t="n">
-        <v>0.06567445167989171</v>
+        <v>0.06577915603473444</v>
       </c>
       <c r="G110" t="n">
-        <v>0.03680052556428893</v>
+        <v>0.03690516909784126</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.04049501652337795</v>
+        <v>0.04046496727148154</v>
       </c>
       <c r="B111" t="n">
-        <v>0.03100133817718858</v>
+        <v>0.03109183889177423</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1616936342891172</v>
+        <v>0.1616334613984841</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2923943037128595</v>
+        <v>0.291476818447174</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3714826406605272</v>
+        <v>0.3722087007294249</v>
       </c>
       <c r="F111" t="n">
-        <v>0.06609819518728242</v>
+        <v>0.06619005929593699</v>
       </c>
       <c r="G111" t="n">
-        <v>0.03683487144964728</v>
+        <v>0.03693415396572435</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.04076717096714556</v>
+        <v>0.0407386922024649</v>
       </c>
       <c r="B112" t="n">
-        <v>0.03118822281965586</v>
+        <v>0.03128798777496595</v>
       </c>
       <c r="C112" t="n">
-        <v>0.16232348961313</v>
+        <v>0.1622776329848091</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2930005243441688</v>
+        <v>0.292064598879536</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3693291730651347</v>
+        <v>0.3700678226789799</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06652292470174447</v>
+        <v>0.06660147664616854</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0368684944890208</v>
+        <v>0.03696178883307545</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.04103456849855942</v>
+        <v>0.04100754444685179</v>
       </c>
       <c r="B113" t="n">
-        <v>0.03136982512268489</v>
+        <v>0.03147916616955673</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1629313367969875</v>
+        <v>0.1628999114791882</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2935303916641037</v>
+        <v>0.292579469644535</v>
       </c>
       <c r="E113" t="n">
-        <v>0.3672832962467623</v>
+        <v>0.3680314085104024</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0669486890977693</v>
+        <v>0.0670138248383427</v>
       </c>
       <c r="G113" t="n">
-        <v>0.03690189257313306</v>
+        <v>0.03698867491112305</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.04129687411023369</v>
+        <v>0.04127108956000818</v>
       </c>
       <c r="B114" t="n">
-        <v>0.03154616399534537</v>
+        <v>0.03166525802681724</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1635180803787741</v>
+        <v>0.1635009873156151</v>
       </c>
       <c r="D114" t="n">
-        <v>0.293956577186424</v>
+        <v>0.2929950188758888</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3653714498985567</v>
+        <v>0.3661249237849306</v>
       </c>
       <c r="F114" t="n">
-        <v>0.06737534110934444</v>
+        <v>0.06742734668451378</v>
       </c>
       <c r="G114" t="n">
-        <v>0.03693551332132165</v>
+        <v>0.03701537575222622</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.04155376473189917</v>
+        <v>0.04152892308486728</v>
       </c>
       <c r="B115" t="n">
-        <v>0.03171734710399598</v>
+        <v>0.03184622939463033</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1640846701310662</v>
+        <v>0.1640816211091549</v>
       </c>
       <c r="D115" t="n">
-        <v>0.2942540406205724</v>
+        <v>0.2932877125027055</v>
       </c>
       <c r="E115" t="n">
-        <v>0.363617889950511</v>
+        <v>0.3643710140825073</v>
       </c>
       <c r="F115" t="n">
-        <v>0.06780253994571869</v>
+        <v>0.06784209483702733</v>
       </c>
       <c r="G115" t="n">
-        <v>0.03696974751623644</v>
+        <v>0.03704240498910732</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.04180493786944574</v>
+        <v>0.04178068229057191</v>
       </c>
       <c r="B116" t="n">
-        <v>0.03188356222984039</v>
+        <v>0.03202212728941861</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1646320684755601</v>
+        <v>0.1646426223945786</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2944012863114903</v>
+        <v>0.2934379425419742</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3620434558690082</v>
+        <v>0.3627884838756773</v>
       </c>
       <c r="F116" t="n">
-        <v>0.06822976470720217</v>
+        <v>0.06825792589233141</v>
       </c>
       <c r="G116" t="n">
-        <v>0.03700492453745295</v>
+        <v>0.03707021571544801</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.04205012027509419</v>
+        <v>0.04202605626684022</v>
       </c>
       <c r="B117" t="n">
-        <v>0.03204506441833468</v>
+        <v>0.03219307470398316</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1651612184228571</v>
+        <v>0.1651848258686834</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2943814964171356</v>
+        <v>0.2934309054712994</v>
       </c>
       <c r="E117" t="n">
-        <v>0.360664452725367</v>
+        <v>0.3613914410516891</v>
       </c>
       <c r="F117" t="n">
-        <v>0.06865633775402635</v>
+        <v>0.06867450468135465</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0370413099871854</v>
+        <v>0.03709919195615018</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.04228907617483827</v>
+        <v>0.04226479443005755</v>
       </c>
       <c r="B118" t="n">
-        <v>0.03220216011178022</v>
+        <v>0.03235926227215517</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1656730142348631</v>
+        <v>0.165709065754966</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2941834604375684</v>
+        <v>0.2932572708860111</v>
       </c>
       <c r="E118" t="n">
-        <v>0.3594917286815051</v>
+        <v>0.3601886461454498</v>
       </c>
       <c r="F118" t="n">
-        <v>0.06908145520965431</v>
+        <v>0.06909131795137237</v>
       </c>
       <c r="G118" t="n">
-        <v>0.03707910514979054</v>
+        <v>0.03712964255998791</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.04252161541690649</v>
+        <v>0.04249671355348558</v>
       </c>
       <c r="B119" t="n">
-        <v>0.03235518951228778</v>
+        <v>0.03252093723084053</v>
       </c>
       <c r="C119" t="n">
-        <v>0.166168275072922</v>
+        <v>0.1662161490917279</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2938022404761907</v>
+        <v>0.2929136122577632</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3585300084343619</v>
+        <v>0.3591830940114609</v>
       </c>
       <c r="F119" t="n">
-        <v>0.06950422294668099</v>
+        <v>0.06950769616403531</v>
       </c>
       <c r="G119" t="n">
-        <v>0.03711844814064999</v>
+        <v>0.03716179769068671</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.04274760076742591</v>
+        <v>0.04272170341758035</v>
       </c>
       <c r="B120" t="n">
-        <v>0.03250450828772699</v>
+        <v>0.03267839039207095</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1666477233806116</v>
+        <v>0.1667068289819918</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2932395332308753</v>
+        <v>0.2924025840929578</v>
       </c>
       <c r="E120" t="n">
-        <v>0.357777523415566</v>
+        <v>0.3583718434489406</v>
       </c>
       <c r="F120" t="n">
-        <v>0.06992369468995958</v>
+        <v>0.0699228417575347</v>
       </c>
       <c r="G120" t="n">
-        <v>0.03715941622783466</v>
+        <v>0.03719580790892371</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.04296695487764735</v>
+        <v>0.04293973112559752</v>
       </c>
       <c r="B121" t="n">
-        <v>0.032650469956575</v>
+        <v>0.03283194186123724</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1671119670862578</v>
+        <v>0.1671817789891872</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2925037074604988</v>
+        <v>0.291732843097422</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3572259606968767</v>
+        <v>0.3577460973032892</v>
       </c>
       <c r="F121" t="n">
-        <v>0.07033891070522987</v>
+        <v>0.07033586196681216</v>
       </c>
       <c r="G121" t="n">
-        <v>0.03720202921691485</v>
+        <v>0.03723174565645505</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.04317966615099369</v>
+        <v>0.04315084406914642</v>
       </c>
       <c r="B122" t="n">
-        <v>0.03279340951970395</v>
+        <v>0.03298192621779645</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1675614863144802</v>
+        <v>0.1676415698384371</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2916095186038142</v>
+        <v>0.290918725519672</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3568607313647171</v>
+        <v>0.3572915213157975</v>
       </c>
       <c r="F122" t="n">
-        <v>0.07074893483789524</v>
+        <v>0.07074580422862285</v>
       </c>
       <c r="G122" t="n">
-        <v>0.03724625320839545</v>
+        <v>0.03726960881052713</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.04338579353133262</v>
+        <v>0.0433551714758591</v>
       </c>
       <c r="B123" t="n">
-        <v>0.03293362943571817</v>
+        <v>0.0331286778272933</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1679966248569595</v>
+        <v>0.1680866494556945</v>
       </c>
       <c r="D123" t="n">
-        <v>0.290577526195671</v>
+        <v>0.2899797084196721</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3566615330712288</v>
+        <v>0.3569887746187734</v>
       </c>
       <c r="F123" t="n">
-        <v>0.07115288805650651</v>
+        <v>0.07115169229946626</v>
       </c>
       <c r="G123" t="n">
-        <v>0.03729200485258332</v>
+        <v>0.03730932590324131</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.04358546978972996</v>
+        <v>0.04355292443752081</v>
       </c>
       <c r="B124" t="n">
-        <v>0.03307138818766389</v>
+        <v>0.03327251689066477</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1684175866607381</v>
+        <v>0.1685173272589892</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2894332675609311</v>
+        <v>0.2889396966261542</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3566031547298117</v>
+        <v>0.3568142107462712</v>
       </c>
       <c r="F124" t="n">
-        <v>0.07154997739324792</v>
+        <v>0.07155256143127475</v>
       </c>
       <c r="G124" t="n">
-        <v>0.03733915567787706</v>
+        <v>0.0373507626091252</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.04377890318069823</v>
+        <v>0.04374439430103391</v>
       </c>
       <c r="B125" t="n">
-        <v>0.0332068918677313</v>
+        <v>0.03341373676362593</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1688244379196464</v>
+        <v>0.1689337635750493</v>
       </c>
       <c r="D125" t="n">
-        <v>0.288206259067926</v>
+        <v>0.2878261849705028</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3566564517656274</v>
+        <v>0.3567406999773211</v>
       </c>
       <c r="F125" t="n">
-        <v>0.07193951952331901</v>
+        <v>0.07194749123246506</v>
       </c>
       <c r="G125" t="n">
-        <v>0.037387536675052</v>
+        <v>0.03739372918000181</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.04396637702318847</v>
+        <v>0.04392994930149384</v>
       </c>
       <c r="B126" t="n">
-        <v>0.033340288898174</v>
+        <v>0.03355259299309721</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1692171149044706</v>
+        <v>0.1693359650695381</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2869289028928933</v>
+        <v>0.2866693428137107</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3567894153903965</v>
+        <v>0.3567385260611606</v>
       </c>
       <c r="F126" t="n">
-        <v>0.07232095768285048</v>
+        <v>0.07233563514503268</v>
       </c>
       <c r="G126" t="n">
-        <v>0.03743694320802629</v>
+        <v>0.03743798861596662</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.04414824734709466</v>
+        <v>0.04411002932653822</v>
       </c>
       <c r="B127" t="n">
-        <v>0.03347166780841743</v>
+        <v>0.03368929441946462</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1695954378280112</v>
+        <v>0.1697237870394066</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2856353614740533</v>
+        <v>0.285501054222743</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3569682728850729</v>
+        <v>0.3567763237753128</v>
       </c>
       <c r="F127" t="n">
-        <v>0.07269387205132451</v>
+        <v>0.07271624575067649</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0374871406060258</v>
+        <v>0.03748326546585797</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.04432493808795216</v>
+        <v>0.04428513873107276</v>
       </c>
       <c r="B128" t="n">
-        <v>0.03360105793995734</v>
+        <v>0.0338239965864629</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1699591304032833</v>
+        <v>0.1700969431858546</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2843604371700039</v>
+        <v>0.2843539265553343</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3571585829457585</v>
+        <v>0.3568220443710637</v>
       </c>
       <c r="F128" t="n">
-        <v>0.07305798291735999</v>
+        <v>0.07308869535080136</v>
       </c>
       <c r="G128" t="n">
-        <v>0.03753787053568466</v>
+        <v>0.0375292552194102</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.04449693424794354</v>
+        <v>0.04445583718017855</v>
       </c>
       <c r="B129" t="n">
-        <v>0.03372843268204091</v>
+        <v>0.0339567975924725</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1703078439529512</v>
+        <v>0.1704550230085868</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2831384650300118</v>
+        <v>0.2832602605835156</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3573263180637539</v>
+        <v>0.3568439559292599</v>
       </c>
       <c r="F129" t="n">
-        <v>0.07341314755927132</v>
+        <v>0.07345249143541287</v>
       </c>
       <c r="G129" t="n">
-        <v>0.03758885846402764</v>
+        <v>0.03757563427057378</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.04466477268810078</v>
+        <v>0.04462272858911852</v>
       </c>
       <c r="B130" t="n">
-        <v>0.03385371490015358</v>
+        <v>0.03408773641511251</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1706411844608903</v>
+        <v>0.1707975163318879</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2820022109481347</v>
+        <v>0.2822509664592083</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3574389436181548</v>
+        <v>0.3568116950350531</v>
       </c>
       <c r="F130" t="n">
-        <v>0.07375935135369034</v>
+        <v>0.07380728677944756</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0376398220308754</v>
+        <v>0.0376220703901722</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.04482903082387511</v>
+        <v>0.04478644834404304</v>
       </c>
       <c r="B131" t="n">
-        <v>0.03397678401300556</v>
+        <v>0.03421679364775824</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1709587417755579</v>
+        <v>0.1711238438657288</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2809817713185848</v>
+        <v>0.2813544213228373</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3574664976152166</v>
+        <v>0.35669737525855</v>
       </c>
       <c r="F131" t="n">
-        <v>0.07409669421458288</v>
+        <v>0.07415288401681719</v>
       </c>
       <c r="G131" t="n">
-        <v>0.03769048023917675</v>
+        <v>0.03766823354426539</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.04499031374150887</v>
+        <v>0.04494764910783556</v>
       </c>
       <c r="B132" t="n">
-        <v>0.03409748428889158</v>
+        <v>0.03434389450268649</v>
       </c>
       <c r="C132" t="n">
-        <v>0.171260117683131</v>
+        <v>0.1714333922445432</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2801034957923544</v>
+        <v>0.280595299834465</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3573826507008447</v>
+        <v>0.3564767228670585</v>
       </c>
       <c r="F132" t="n">
-        <v>0.07442537474048828</v>
+        <v>0.07448923469637266</v>
       </c>
       <c r="G132" t="n">
-        <v>0.03774056305278154</v>
+        <v>0.03771380674703854</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.04514923966058738</v>
+        <v>0.04510698562540249</v>
       </c>
       <c r="B133" t="n">
-        <v>0.0342156338379537</v>
+        <v>0.03446891385708223</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1715449522836342</v>
+        <v>0.1717255516815948</v>
       </c>
       <c r="D133" t="n">
-        <v>0.279388990545172</v>
+        <v>0.2799934579476789</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3571656900060944</v>
+        <v>0.3561301613416556</v>
       </c>
       <c r="F133" t="n">
-        <v>0.07474567292203099</v>
+        <v>0.0748164330578035</v>
       </c>
       <c r="G133" t="n">
-        <v>0.03778982074452745</v>
+        <v>0.03775849648878233</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.04530642467022318</v>
+        <v>0.04526509903124302</v>
       </c>
       <c r="B134" t="n">
-        <v>0.03433103387764428</v>
+        <v>0.03459168304891048</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1718129464884235</v>
+        <v>0.1719997541720126</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2788542826502708</v>
+        <v>0.2795629874701053</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3567993460591549</v>
+        <v>0.3556437290128254</v>
       </c>
       <c r="F134" t="n">
-        <v>0.07505793377133207</v>
+        <v>0.07513470507391647</v>
       </c>
       <c r="G134" t="n">
-        <v>0.03783803248295119</v>
+        <v>0.0378020421909869</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.04546246683084547</v>
+        <v>0.04542260122908712</v>
       </c>
       <c r="B135" t="n">
-        <v>0.03444347785678165</v>
+        <v>0.03471199807651451</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1720638795459857</v>
+        <v>0.1722555100554614</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2785092280159681</v>
+        <v>0.2793115596991724</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3562733817909597</v>
+        <v>0.3550097131555923</v>
       </c>
       <c r="F135" t="n">
-        <v>0.07536255258700109</v>
+        <v>0.07544439363327711</v>
       </c>
       <c r="G135" t="n">
-        <v>0.03788501337245834</v>
+        <v>0.03784422415089495</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.0456179306784676</v>
+        <v>0.04558005994992777</v>
       </c>
       <c r="B136" t="n">
-        <v>0.03455276013042274</v>
+        <v>0.03482962882810292</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1722976213496645</v>
+        <v>0.1724924407425411</v>
       </c>
       <c r="D136" t="n">
-        <v>0.2783572169253493</v>
+        <v>0.2792401374134691</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3555838882807242</v>
+        <v>0.3542269225344492</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0756599629918194</v>
+        <v>0.07574594099628365</v>
       </c>
       <c r="G136" t="n">
-        <v>0.03793061964355238</v>
+        <v>0.03788486953522621</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0.04577333240874712</v>
+        <v>0.04573798509001784</v>
       </c>
       <c r="B137" t="n">
-        <v>0.03465868394462792</v>
+        <v>0.03494432896717986</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1725141389435791</v>
+        <v>0.172710305580017</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2783951950330519</v>
+        <v>0.2793430760697724</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3547332702629644</v>
+        <v>0.3533005783841307</v>
       </c>
       <c r="F137" t="n">
-        <v>0.07595062790909807</v>
+        <v>0.07603986978179059</v>
       </c>
       <c r="G137" t="n">
-        <v>0.03797475149793146</v>
+        <v>0.03792385612709163</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.04592912667796625</v>
+        <v>0.0458968168741342</v>
       </c>
       <c r="B138" t="n">
-        <v>0.03476106853549881</v>
+        <v>0.03505584612241495</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1727134978088738</v>
+        <v>0.1729090212093019</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2786139812256023</v>
+        <v>0.2796085827882644</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3537299387416579</v>
+        <v>0.3522418556147967</v>
       </c>
       <c r="F138" t="n">
-        <v>0.07623503332523095</v>
+        <v>0.07632676370108982</v>
       </c>
       <c r="G138" t="n">
-        <v>0.03801735368516951</v>
+        <v>0.03796111368999847</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.04608569523072342</v>
+        <v>0.04605691628815828</v>
       </c>
       <c r="B139" t="n">
-        <v>0.03485975519239753</v>
+        <v>0.0351639320631324</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1728958585415031</v>
+        <v>0.1730886723551691</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2789988429562989</v>
+        <v>0.2800194692380744</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3525877503082475</v>
+        <v>0.3510671380094078</v>
       </c>
       <c r="F139" t="n">
-        <v>0.07651368398305262</v>
+        <v>0.07660724906852302</v>
       </c>
       <c r="G139" t="n">
-        <v>0.03805841378777704</v>
+        <v>0.03799662297753491</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.04624333807222666</v>
+        <v>0.0462185580955221</v>
       </c>
       <c r="B140" t="n">
-        <v>0.03495461224090537</v>
+        <v>0.03526835257273259</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1730614708998348</v>
+        <v>0.1732495137010313</v>
       </c>
       <c r="D140" t="n">
-        <v>0.2795302770184342</v>
+        <v>0.2805541214710557</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3513252429078099</v>
+        <v>0.3497970637527928</v>
       </c>
       <c r="F140" t="n">
-        <v>0.07678710024108679</v>
+        <v>0.07688197782767096</v>
       </c>
       <c r="G140" t="n">
-        <v>0.03809795861970238</v>
+        <v>0.03803041257919419</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.04640226772676934</v>
+        <v>0.04638192661741052</v>
       </c>
       <c r="B141" t="n">
-        <v>0.03504553888750443</v>
+        <v>0.03536889675494687</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1732106651192418</v>
+        <v>0.1733919632602398</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2801849432761629</v>
+        <v>0.2811876092762819</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3499647201714927</v>
+        <v>0.3484554376583614</v>
       </c>
       <c r="F141" t="n">
-        <v>0.07705581559165599</v>
+        <v>0.07715161249614091</v>
       </c>
       <c r="G141" t="n">
-        <v>0.03813604922717284</v>
+        <v>0.03806255393661806</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.04656260599137674</v>
+        <v>0.04654711433356445</v>
       </c>
       <c r="B142" t="n">
-        <v>0.03513246805883185</v>
+        <v>0.03546538551975578</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1733438425650541</v>
+        <v>0.1735165883184732</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2809367004459603</v>
+        <v>0.2818928633347182</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3485312355733731</v>
+        <v>0.3470680804119108</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0773203725740092</v>
+        <v>0.07741681311208688</v>
       </c>
       <c r="G142" t="n">
-        <v>0.03817277479139496</v>
+        <v>0.03809315496949101</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.04672438409678188</v>
+        <v>0.04671412325830191</v>
       </c>
       <c r="B143" t="n">
-        <v>0.03521536820140153</v>
+        <v>0.0355576789997121</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1734614661892586</v>
+        <v>0.1736240855061522</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2817576928465944</v>
+        <v>0.2826418568335944</v>
       </c>
       <c r="E143" t="n">
-        <v>0.34705152466152</v>
+        <v>0.345661676585611</v>
       </c>
       <c r="F143" t="n">
-        <v>0.07758131786990995</v>
+        <v>0.07767822601049773</v>
       </c>
       <c r="G143" t="n">
-        <v>0.03820824613453368</v>
+        <v>0.03812235280613059</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.04688754555624308</v>
+        <v>0.0468828689661662</v>
       </c>
       <c r="B144" t="n">
-        <v>0.03529424422817225</v>
+        <v>0.03564568265037795</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1735640513787682</v>
+        <v>0.1737152568244766</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2826194438724287</v>
+        <v>0.2834067380861146</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3455529307602127</v>
+        <v>0.3442626732579337</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07783919506246238</v>
+        <v>0.07793647409460892</v>
       </c>
       <c r="G144" t="n">
-        <v>0.03824258914171282</v>
+        <v>0.03815030612032198</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.04705195186035523</v>
+        <v>0.04705318707888696</v>
       </c>
       <c r="B145" t="n">
-        <v>0.03536913767986954</v>
+        <v>0.03572935180127348</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1736521572285675</v>
+        <v>0.17379098351403</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2834939125731626</v>
+        <v>0.2841608718296641</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3440623662997355</v>
+        <v>0.3428962700389159</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0780945358151305</v>
+        <v>0.07819214819588044</v>
       </c>
       <c r="G145" t="n">
-        <v>0.03827593854317898</v>
+        <v>0.03817718754134947</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.04721739069741763</v>
+        <v>0.04722484197225443</v>
       </c>
       <c r="B146" t="n">
-        <v>0.03544012620922968</v>
+        <v>0.03580869445724524</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1737263786597764</v>
+        <v>0.173852199561063</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2843544764984786</v>
+        <v>0.2848797586718102</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3426053460383203</v>
+        <v>0.3415855296799139</v>
       </c>
       <c r="F146" t="n">
-        <v>0.07834784955877558</v>
+        <v>0.07844579912022435</v>
       </c>
       <c r="G146" t="n">
-        <v>0.03830843233800236</v>
+        <v>0.03820317653748882</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.04738358612064392</v>
+        <v>0.04739753740829504</v>
       </c>
       <c r="B147" t="n">
-        <v>0.03550732251116534</v>
+        <v>0.03588377220792152</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1737873390012996</v>
+        <v>0.1738998664192719</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2851768097086574</v>
+        <v>0.2855418132672022</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3412051236653344</v>
+        <v>0.3403506275692267</v>
       </c>
       <c r="F147" t="n">
-        <v>0.07859961201706475</v>
+        <v>0.07869793004375709</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0383402069758344</v>
+        <v>0.03822845308432556</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.04755021025614382</v>
+        <v>0.04757092873722325</v>
       </c>
       <c r="B148" t="n">
-        <v>0.03557087269256161</v>
+        <v>0.035954699182753</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1738356828582754</v>
+        <v>0.1739349502012162</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2859396302421128</v>
+        <v>0.2861289904869891</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3398819571844625</v>
+        <v>0.3392082500165163</v>
       </c>
       <c r="F148" t="n">
-        <v>0.07885025343667279</v>
+        <v>0.07894898904755195</v>
       </c>
       <c r="G148" t="n">
-        <v>0.03837139332977121</v>
+        <v>0.03825319232775007</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.0477168963008503</v>
+        <v>0.04774463624210949</v>
       </c>
       <c r="B149" t="n">
-        <v>0.03563095415130223</v>
+        <v>0.03602163908135713</v>
       </c>
       <c r="C149" t="n">
-        <v>0.173872068963587</v>
+        <v>0.1739584021950477</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2866252962947745</v>
+        <v>0.286627253806962</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3386525231191987</v>
+        <v>0.3381711465648302</v>
       </c>
       <c r="F149" t="n">
-        <v>0.07910014755516029</v>
+        <v>0.07919936176263963</v>
       </c>
       <c r="G149" t="n">
-        <v>0.03840211361512685</v>
+        <v>0.03827756034705374</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.04788325212609493</v>
+        <v>0.04791825912337466</v>
       </c>
       <c r="B150" t="n">
-        <v>0.03568777285381126</v>
+        <v>0.03608480040278708</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1738971630688766</v>
+        <v>0.1739711431368629</v>
       </c>
       <c r="D150" t="n">
-        <v>0.287220235900277</v>
+        <v>0.2870268814207493</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3375294950654357</v>
+        <v>0.3372478405725328</v>
       </c>
       <c r="F150" t="n">
-        <v>0.07934960193775902</v>
+        <v>0.07944936431850599</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0384324790477461</v>
+        <v>0.03830171102518717</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.04804887394814295</v>
+        <v>0.04809138955406216</v>
       </c>
       <c r="B151" t="n">
-        <v>0.03574156008357215</v>
+        <v>0.03614443008289293</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1739116302163678</v>
+        <v>0.1739740512842443</v>
       </c>
       <c r="D151" t="n">
-        <v>0.2877151980226895</v>
+        <v>0.2873226048054103</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3365212992960958</v>
+        <v>0.3364425033180377</v>
       </c>
       <c r="F151" t="n">
-        <v>0.07959885013981702</v>
+        <v>0.07969923700660302</v>
       </c>
       <c r="G151" t="n">
-        <v>0.03846258829331465</v>
+        <v>0.03832578394874971</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.04821335960609639</v>
+        <v>0.0482636261985935</v>
       </c>
       <c r="B152" t="n">
-        <v>0.03579256841174736</v>
+        <v>0.03620080581856116</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1739161271226157</v>
+        <v>0.1739679540552304</v>
       </c>
       <c r="D152" t="n">
-        <v>0.2881053180000616</v>
+        <v>0.2875135742544319</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3356320537213604</v>
+        <v>0.3357549972443937</v>
       </c>
       <c r="F152" t="n">
-        <v>0.07984804667245268</v>
+        <v>0.0799491392334368</v>
       </c>
       <c r="G152" t="n">
-        <v>0.03849252646566572</v>
+        <v>0.03834990319535254</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.04837632097422673</v>
+        <v>0.04843458659417898</v>
       </c>
       <c r="B153" t="n">
-        <v>0.03584106697160919</v>
+        <v>0.03625422740750861</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1739112947345502</v>
+        <v>0.1739536228426136</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2883899972618443</v>
+        <v>0.2876031486899524</v>
       </c>
       <c r="E153" t="n">
-        <v>0.3348616904832178</v>
+        <v>0.3351810912417818</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0800972648561534</v>
+        <v>0.08019914639907202</v>
       </c>
       <c r="G153" t="n">
-        <v>0.03852236471839831</v>
+        <v>0.0383741768248923</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.04853739490968489</v>
+        <v>0.04860391785428724</v>
       </c>
       <c r="B154" t="n">
-        <v>0.03588733597099099</v>
+        <v>0.03630500746110148</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1738977508377476</v>
+        <v>0.1739317705730099</v>
       </c>
       <c r="D154" t="n">
-        <v>0.2885726054649662</v>
+        <v>0.2875985139287828</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3342062549462753</v>
+        <v>0.3347128440276922</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0803464976699271</v>
+        <v>0.08044924928094394</v>
       </c>
       <c r="G154" t="n">
-        <v>0.03855216020040782</v>
+        <v>0.03839869687418304</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.04869625273776323</v>
+        <v>0.04877130526566031</v>
       </c>
       <c r="B155" t="n">
-        <v>0.03593166050250553</v>
+        <v>0.03635346185601248</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1738760842664659</v>
+        <v>0.1739030516071927</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2886600223734819</v>
+        <v>0.2875101438340455</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3336583615105249</v>
+        <v>0.3343391414275675</v>
       </c>
       <c r="F155" t="n">
-        <v>0.08059566219339487</v>
+        <v>0.08069935634646853</v>
       </c>
       <c r="G155" t="n">
-        <v>0.03858195641586374</v>
+        <v>0.03842353966305296</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.04885260763688298</v>
+        <v>0.04893647850092639</v>
       </c>
       <c r="B156" t="n">
-        <v>0.03597432379509873</v>
+        <v>0.03639990028150415</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1738468506588171</v>
+        <v>0.1738680636229898</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2886620476835999</v>
+        <v>0.2873511304562437</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3332077797003252</v>
+        <v>0.3340463616973754</v>
       </c>
       <c r="F156" t="n">
-        <v>0.08084460674042954</v>
+        <v>0.08094929919019035</v>
       </c>
       <c r="G156" t="n">
-        <v>0.03861178378484661</v>
+        <v>0.03844876625076989</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.04900621996948918</v>
+        <v>0.04909921534004345</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0360156001364954</v>
+        <v>0.03644461722002432</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1738105705023774</v>
+        <v>0.1738273511468001</v>
       </c>
       <c r="D157" t="n">
-        <v>0.2885907143088134</v>
+        <v>0.2871364199507916</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3328421141287269</v>
+        <v>0.3338191323842436</v>
       </c>
       <c r="F157" t="n">
-        <v>0.08109312057458369</v>
+        <v>0.08119884102961072</v>
       </c>
       <c r="G157" t="n">
-        <v>0.03864166037951374</v>
+        <v>0.03847442292848607</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.0491569005961812</v>
+        <v>0.04925934296459699</v>
       </c>
       <c r="B158" t="n">
-        <v>0.03605574771976699</v>
+        <v>0.03648788367808613</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1737677299019784</v>
+        <v>0.1737814103843678</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2884595446968487</v>
+        <v>0.2868819986710028</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3325475385614853</v>
+        <v>0.3336411346898478</v>
       </c>
       <c r="F158" t="n">
-        <v>0.08134094570850789</v>
+        <v>0.08144768792613492</v>
       </c>
       <c r="G158" t="n">
-        <v>0.03867159281523132</v>
+        <v>0.03850054168596358</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.04930451210175038</v>
+        <v>0.04941673704178465</v>
       </c>
       <c r="B159" t="n">
-        <v>0.03609500177522784</v>
+        <v>0.03652993996680098</v>
       </c>
       <c r="C159" t="n">
-        <v>0.173718783991604</v>
+        <v>0.1737306949543138</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2882827935722924</v>
+        <v>0.286604077110245</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3323095416317847</v>
+        <v>0.3334959081358611</v>
       </c>
       <c r="F159" t="n">
-        <v>0.08158778974059902</v>
+        <v>0.08169550215242509</v>
       </c>
       <c r="G159" t="n">
-        <v>0.03870157718674198</v>
+        <v>0.03852714063856942</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>0.04944896809245116</v>
+        <v>0.0495713189348747</v>
       </c>
       <c r="B160" t="n">
-        <v>0.03613356832884954</v>
+        <v>0.0365709898140311</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1736641624459875</v>
+        <v>0.1736756220678057</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2880747176060491</v>
+        <v>0.2863183179972415</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3321136445658003</v>
+        <v>0.3333676098171223</v>
       </c>
       <c r="F160" t="n">
-        <v>0.08183333894860546</v>
+        <v>0.08194191693160856</v>
       </c>
       <c r="G160" t="n">
-        <v>0.03873160001225665</v>
+        <v>0.03855422443731617</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0.04959023087285935</v>
+        <v>0.04972305145588526</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0361716189712744</v>
+        <v>0.03661119606357931</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1736042769284664</v>
+        <v>0.1736165786553955</v>
       </c>
       <c r="D161" t="n">
-        <v>0.2878489091328197</v>
+        <v>0.2860391493768585</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3319460540576655</v>
+        <v>0.3332416880874394</v>
       </c>
       <c r="F161" t="n">
-        <v>0.08207727079036997</v>
+        <v>0.08218655165333791</v>
       </c>
       <c r="G161" t="n">
-        <v>0.03876163924654445</v>
+        <v>0.03858178470750412</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0.04972830761908295</v>
+        <v>0.04987193361073283</v>
       </c>
       <c r="B162" t="n">
-        <v>0.03620928691464901</v>
+        <v>0.0366506781700383</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1735395290727427</v>
+        <v>0.1735539269450165</v>
       </c>
       <c r="D162" t="n">
-        <v>0.287617725080443</v>
+        <v>0.2857791950302395</v>
       </c>
       <c r="E162" t="n">
-        <v>0.3317942211477488</v>
+        <v>0.3331054390301042</v>
       </c>
       <c r="F162" t="n">
-        <v>0.08231926489652663</v>
+        <v>0.08242902664130586</v>
       </c>
       <c r="G162" t="n">
-        <v>0.03879166526880682</v>
+        <v>0.03860980057256308</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0.04986324550723231</v>
+        <v>0.0500179947797511</v>
       </c>
       <c r="B163" t="n">
-        <v>0.03624666461121152</v>
+        <v>0.03668951162440361</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1734703184988982</v>
+        <v>0.1734880090594177</v>
       </c>
       <c r="D163" t="n">
-        <v>0.28739183485966</v>
+        <v>0.2855488444537892</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3316472823707062</v>
+        <v>0.3329484241541657</v>
       </c>
       <c r="F163" t="n">
-        <v>0.08255901218403792</v>
+        <v>0.08266897660688872</v>
       </c>
       <c r="G163" t="n">
-        <v>0.03882164196825358</v>
+        <v>0.03863823932158392</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0.0499951259913606</v>
+        <v>0.05016128873448827</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0362838030534175</v>
+        <v>0.0367277293479242</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1733970493859017</v>
+        <v>0.1734191503238613</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2871799038896748</v>
+        <v>0.2853559741205003</v>
       </c>
       <c r="E164" t="n">
-        <v>0.3314963681917468</v>
+        <v>0.3327627381371772</v>
       </c>
       <c r="F164" t="n">
-        <v>0.08279622165237037</v>
+        <v>0.08290606206183204</v>
       </c>
       <c r="G164" t="n">
-        <v>0.03885152783552832</v>
+        <v>0.03866705727421679</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>0.05012405864510505</v>
+        <v>0.05030188782533587</v>
       </c>
       <c r="B165" t="n">
-        <v>0.03632071283574921</v>
+        <v>0.03676532497877412</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1733201353645389</v>
+        <v>0.1733476611329081</v>
       </c>
       <c r="D165" t="n">
-        <v>0.2869884200203215</v>
+        <v>0.2852058219657416</v>
       </c>
       <c r="E165" t="n">
-        <v>0.331334771168408</v>
+        <v>0.3325431250529599</v>
       </c>
       <c r="F165" t="n">
-        <v>0.08303062479986333</v>
+        <v>0.08313997815960271</v>
       </c>
       <c r="G165" t="n">
-        <v>0.03888127716601412</v>
+        <v>0.0386962008846778</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>0.05025017484168844</v>
+        <v>0.05043987759435824</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0363573669161128</v>
+        <v>0.03680225786100459</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1732400018182444</v>
+        <v>0.1732738373869067</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2868216630521784</v>
+        <v>0.2851010086986583</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3311579743977242</v>
+        <v>0.3322869496841491</v>
       </c>
       <c r="F166" t="n">
-        <v>0.08326197765345465</v>
+        <v>0.08337046066760601</v>
       </c>
       <c r="G166" t="n">
-        <v>0.03891084132059749</v>
+        <v>0.03872560810731727</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>0.05037362171060376</v>
+        <v>0.05057535198549463</v>
       </c>
       <c r="B167" t="n">
-        <v>0.03639370495509719</v>
+        <v>0.03683845943832419</v>
       </c>
       <c r="C167" t="n">
-        <v>0.1731570853780601</v>
+        <v>0.1731979596487145</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2866818081457126</v>
+        <v>0.2850416929298304</v>
       </c>
       <c r="E167" t="n">
-        <v>0.330963548683537</v>
+        <v>0.331994036957915</v>
       </c>
       <c r="F167" t="n">
-        <v>0.08349006104201227</v>
+        <v>0.0835972890189919</v>
       </c>
       <c r="G167" t="n">
-        <v>0.03894017008497699</v>
+        <v>0.03875521002072969</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0.05049455638058675</v>
+        <v>0.05070840924736023</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0364296389446741</v>
+        <v>0.03687384066632114</v>
       </c>
       <c r="C168" t="n">
-        <v>0.1730718309373354</v>
+        <v>0.1731202912692272</v>
       </c>
       <c r="D168" t="n">
-        <v>0.2865691472357514</v>
+        <v>0.2850258421167022</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3307509345144913</v>
+        <v>0.3316663973903736</v>
       </c>
       <c r="F168" t="n">
-        <v>0.08371467899571329</v>
+        <v>0.08382028663209487</v>
       </c>
       <c r="G168" t="n">
-        <v>0.03896921299144745</v>
+        <v>0.03878493267792113</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0.05061314097116332</v>
+        <v>0.05083914855934466</v>
       </c>
       <c r="B169" t="n">
-        <v>0.03646505977955369</v>
+        <v>0.03690829999348995</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1729846861886014</v>
+        <v>0.1730410757853114</v>
       </c>
       <c r="D169" t="n">
-        <v>0.2864824053772685</v>
+        <v>0.2850495976028893</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3305211305564002</v>
+        <v>0.3313078600417546</v>
       </c>
       <c r="F169" t="n">
-        <v>0.08393565653438891</v>
+        <v>0.08403931889710867</v>
       </c>
       <c r="G169" t="n">
-        <v>0.03899792059262405</v>
+        <v>0.03881469912010135</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.05072953834737887</v>
+        <v>0.05096766736177318</v>
       </c>
       <c r="B170" t="n">
-        <v>0.03649984444908286</v>
+        <v>0.0369417314302088</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1728960944205643</v>
+        <v>0.1729605339056444</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2864191245187954</v>
+        <v>0.2851077092610521</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3302763155851811</v>
+        <v>0.3309236371817748</v>
       </c>
       <c r="F170" t="n">
-        <v>0.08415283702972333</v>
+        <v>0.08425428939533904</v>
       </c>
       <c r="G170" t="n">
-        <v>0.03902624564927415</v>
+        <v>0.03884443146420716</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.0508439086066908</v>
+        <v>0.05109405933721729</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0365338634611781</v>
+        <v>0.03697403222850867</v>
       </c>
       <c r="C171" t="n">
-        <v>0.172806485514027</v>
+        <v>0.1728788603787556</v>
       </c>
       <c r="D171" t="n">
-        <v>0.2863760850522897</v>
+        <v>0.2851940133768262</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3300194336449928</v>
+        <v>0.3305198467050816</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0843660796205002</v>
+        <v>0.08446513501883589</v>
       </c>
       <c r="G171" t="n">
-        <v>0.03905414410032118</v>
+        <v>0.03887405295477463</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0.05095640636628663</v>
+        <v>0.05121841297026167</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0365669879965948</v>
+        <v>0.03700510973429486</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1727162661126341</v>
+        <v>0.1727962209976486</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2863497352323699</v>
+        <v>0.28530192661224</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3297537709857984</v>
+        <v>0.3301030191393132</v>
       </c>
       <c r="F172" t="n">
-        <v>0.08457525753393406</v>
+        <v>0.08467182068310523</v>
       </c>
       <c r="G172" t="n">
-        <v>0.03908157577238203</v>
+        <v>0.03890348986313653</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0.05106717885286132</v>
+        <v>0.05134081060575437</v>
       </c>
       <c r="B173" t="n">
-        <v>0.03659909652529546</v>
+        <v>0.03703488704394373</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1726258093594839</v>
+        <v>0.1727127499536497</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2863365999533018</v>
+        <v>0.2854249293700383</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3294825528573738</v>
+        <v>0.3296796156360219</v>
       </c>
       <c r="F173" t="n">
-        <v>0.08478025756999477</v>
+        <v>0.08487433426548724</v>
       </c>
       <c r="G173" t="n">
-        <v>0.03910850488168918</v>
+        <v>0.03893267312510448</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0.05117636457411802</v>
+        <v>0.05146132792572886</v>
       </c>
       <c r="B174" t="n">
-        <v>0.03663008056150108</v>
+        <v>0.03706330719311746</v>
       </c>
       <c r="C174" t="n">
-        <v>0.1725354445020993</v>
+        <v>0.172628547725973</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2863336455774222</v>
+        <v>0.2855570136862157</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3292085837811736</v>
+        <v>0.3292555815767753</v>
       </c>
       <c r="F174" t="n">
-        <v>0.08498098070374929</v>
+        <v>0.08507268226102872</v>
       </c>
       <c r="G174" t="n">
-        <v>0.03913490029993627</v>
+        <v>0.03896153963116115</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0.05128409259251586</v>
+        <v>0.05158003377080333</v>
       </c>
       <c r="B175" t="n">
-        <v>0.03665984924124984</v>
+        <v>0.03709033571951388</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1724454472373159</v>
+        <v>0.172543679688975</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2863385811899423</v>
+        <v>0.2856930736885239</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3289339499422713</v>
+        <v>0.328835957563873</v>
       </c>
       <c r="F175" t="n">
-        <v>0.08517734419554139</v>
+        <v>0.08526688645034423</v>
       </c>
       <c r="G175" t="n">
-        <v>0.03916073560116323</v>
+        <v>0.03899003311796601</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.05139048217816759</v>
+        <v>0.05169699023881394</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0366883326858844</v>
+        <v>0.03711596156315042</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1723560311718402</v>
+        <v>0.1724581756259124</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2863500834862363</v>
+        <v>0.285829220371893</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3286597970094146</v>
+        <v>0.3284245658875469</v>
       </c>
       <c r="F176" t="n">
-        <v>0.08536928445744886</v>
+        <v>0.08545698166268924</v>
       </c>
       <c r="G176" t="n">
-        <v>0.03918598901100822</v>
+        <v>0.03901810464999432</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.05149564273120871</v>
+        <v>0.05181225299914408</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0367154839879876</v>
+        <v>0.03714019638691814</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1722673410845271</v>
+        <v>0.1723720303290466</v>
       </c>
       <c r="D177" t="n">
-        <v>0.2863679378244903</v>
+        <v>0.2859630067269771</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3283861905247497</v>
+        <v>0.3280237862965297</v>
       </c>
       <c r="F177" t="n">
-        <v>0.08555676060478247</v>
+        <v>0.08564301454256118</v>
       </c>
       <c r="G177" t="n">
-        <v>0.03921064324225424</v>
+        <v>0.03904571271882323</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.05159967393259414</v>
+        <v>0.05192587176418263</v>
       </c>
       <c r="B178" t="n">
-        <v>0.03674127987933974</v>
+        <v>0.03716307250715688</v>
       </c>
       <c r="C178" t="n">
-        <v>0.172179448411611</v>
+        <v>0.1722852054142549</v>
       </c>
       <c r="D178" t="n">
-        <v>0.2863930932662392</v>
+        <v>0.2860935540361836</v>
       </c>
       <c r="E178" t="n">
-        <v>0.328112060926579</v>
+        <v>0.327634430129388</v>
       </c>
       <c r="F178" t="n">
-        <v>0.08573975826222377</v>
+        <v>0.08582504312898988</v>
       </c>
       <c r="G178" t="n">
-        <v>0.03923468532141355</v>
+        <v>0.03907282301984398</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.05170266596672982</v>
+        <v>0.05203789085972301</v>
       </c>
       <c r="B179" t="n">
-        <v>0.03676572015005083</v>
+        <v>0.03718463971109539</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1720923496894634</v>
+        <v>0.1721976323818143</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2864276349340087</v>
+        <v>0.2862215754067211</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3278352296070064</v>
+        <v>0.3272557166181492</v>
       </c>
       <c r="F179" t="n">
-        <v>0.08591829319284862</v>
+        <v>0.08600313703479223</v>
       </c>
       <c r="G179" t="n">
-        <v>0.03925810645989253</v>
+        <v>0.03909940798770536</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.0518046995399311</v>
+        <v>0.05214834983622079</v>
       </c>
       <c r="B180" t="n">
-        <v>0.03678882601334074</v>
+        <v>0.03720496130002731</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1720059678745783</v>
+        <v>0.1721092168372118</v>
       </c>
       <c r="D180" t="n">
-        <v>0.2864746804866889</v>
+        <v>0.2863492982339484</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3275525101192484</v>
+        <v>0.3268853495730956</v>
       </c>
       <c r="F180" t="n">
-        <v>0.08609241406808064</v>
+        <v>0.08617737803760847</v>
       </c>
       <c r="G180" t="n">
-        <v>0.03928090189813167</v>
+        <v>0.039125446181888</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.05190584590605225</v>
+        <v>0.05225728406495485</v>
       </c>
       <c r="B181" t="n">
-        <v>0.03681063756146805</v>
+        <v>0.0372241097307563</v>
       </c>
       <c r="C181" t="n">
-        <v>0.1719201569567618</v>
+        <v>0.1720198436818423</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2865382101682925</v>
+        <v>0.2864802930158502</v>
       </c>
       <c r="E181" t="n">
-        <v>0.3272598738142071</v>
+        <v>0.3265196869721455</v>
       </c>
       <c r="F181" t="n">
-        <v>0.08626220473703752</v>
+        <v>0.08634786092197523</v>
       </c>
       <c r="G181" t="n">
-        <v>0.039303070856181</v>
+        <v>0.03915092161247566</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.05200616659053217</v>
+        <v>0.05236472527107033</v>
       </c>
       <c r="B182" t="n">
-        <v>0.03683121056547137</v>
+        <v>0.03724216223089332</v>
       </c>
       <c r="C182" t="n">
-        <v>0.1718347093773574</v>
+        <v>0.171929383020622</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2866228435599307</v>
+        <v>0.2866192213463577</v>
       </c>
       <c r="E182" t="n">
-        <v>0.3269526680711455</v>
+        <v>0.3261539906291234</v>
       </c>
       <c r="F182" t="n">
-        <v>0.08642778535329831</v>
+        <v>0.08651469441577544</v>
       </c>
       <c r="G182" t="n">
-        <v>0.03932461648226426</v>
+        <v>0.03917582308615786</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.05210571297899118</v>
+        <v>0.05247070196681237</v>
       </c>
       <c r="B183" t="n">
-        <v>0.03685061285175131</v>
+        <v>0.03725919673585528</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1717493662076146</v>
+        <v>0.1718376965059852</v>
       </c>
       <c r="D183" t="n">
-        <v>0.2867335760836929</v>
+        <v>0.2867715205081484</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3266258734066175</v>
+        <v>0.3257827385981668</v>
       </c>
       <c r="F183" t="n">
-        <v>0.08658931260748776</v>
+        <v>0.08667800204943744</v>
       </c>
       <c r="G183" t="n">
-        <v>0.03934554586384467</v>
+        <v>0.03920014363559424</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0.05220452561930094</v>
+        <v>0.05257523976362218</v>
       </c>
       <c r="B184" t="n">
-        <v>0.03686892051558163</v>
+        <v>0.03727528843932243</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1716638292786538</v>
+        <v>0.1717446438327207</v>
       </c>
       <c r="D184" t="n">
-        <v>0.2868754911662945</v>
+        <v>0.2869430454175932</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3262743847162489</v>
+        <v>0.3253999797152921</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0867469786937211</v>
+        <v>0.08683792275631949</v>
       </c>
       <c r="G184" t="n">
-        <v>0.03936587001019921</v>
+        <v>0.0392238800751304</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.05230263343631544</v>
+        <v>0.05267836155624969</v>
       </c>
       <c r="B185" t="n">
-        <v>0.03688621416015674</v>
+        <v>0.03729050717078052</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1715777744402538</v>
+        <v>0.1716500890935714</v>
       </c>
       <c r="D185" t="n">
-        <v>0.2870534633377065</v>
+        <v>0.2871396904262792</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3258933014577925</v>
+        <v>0.3249997080006314</v>
       </c>
       <c r="F185" t="n">
-        <v>0.08690100933654388</v>
+        <v>0.08699461104910435</v>
       </c>
       <c r="G185" t="n">
-        <v>0.03938560383123089</v>
+        <v>0.03924703270338328</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.05240005298726087</v>
+        <v>0.05278008758515953</v>
       </c>
       <c r="B186" t="n">
-        <v>0.03690257538020451</v>
+        <v>0.03730491572170786</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1714908654206944</v>
+        <v>0.1715539066994972</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2872718674460814</v>
+        <v>0.2873670135313018</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3254782116264837</v>
+        <v>0.3245762346528704</v>
       </c>
       <c r="F186" t="n">
-        <v>0.08705166099215626</v>
+        <v>0.08714823665755299</v>
       </c>
       <c r="G186" t="n">
-        <v>0.03940476614711893</v>
+        <v>0.03926960515191028</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.05249678777260321</v>
+        <v>0.05288043539278193</v>
       </c>
       <c r="B187" t="n">
-        <v>0.03691808368434756</v>
+        <v>0.0373185691459271</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1714027667866325</v>
+        <v>0.1714559865675409</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2875343090788004</v>
+        <v>0.2876298839736756</v>
       </c>
       <c r="E187" t="n">
-        <v>0.3250254559559524</v>
+        <v>0.3241245369759821</v>
       </c>
       <c r="F187" t="n">
-        <v>0.08719921706803289</v>
+        <v>0.0872989835844547</v>
       </c>
       <c r="G187" t="n">
-        <v>0.03942337965363087</v>
+        <v>0.03929160435963782</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.05259282774958056</v>
+        <v>0.05297941969565585</v>
       </c>
       <c r="B188" t="n">
-        <v>0.03693281391119191</v>
+        <v>0.037331514968625</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1713131557688859</v>
+        <v>0.1713562382995704</v>
       </c>
       <c r="D188" t="n">
-        <v>0.2878433884244536</v>
+        <v>0.2879321712660241</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3245323597684511</v>
+        <v>0.3236405665212665</v>
       </c>
       <c r="F188" t="n">
-        <v>0.08734398354787244</v>
+        <v>0.0874470486109013</v>
       </c>
       <c r="G188" t="n">
-        <v>0.03944147082956469</v>
+        <v>0.03931304063795669</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0.05268814933674398</v>
+        <v>0.05307705219746484</v>
       </c>
       <c r="B189" t="n">
-        <v>0.03694683430637487</v>
+        <v>0.03734379416165178</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1712217318309261</v>
+        <v>0.1712545941218986</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2882005075978534</v>
+        <v>0.2882764897763586</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3239974226403912</v>
+        <v>0.3231215026237501</v>
       </c>
       <c r="F189" t="n">
-        <v>0.08748628439681559</v>
+        <v>0.08759263933779608</v>
       </c>
       <c r="G189" t="n">
-        <v>0.03945906989089462</v>
+        <v>0.03933392778108027</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0.05278271567540561</v>
+        <v>0.05317334136923556</v>
       </c>
       <c r="B190" t="n">
-        <v>0.03696020526449429</v>
+        <v>0.03735544268523484</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1711282236760731</v>
+        <v>0.1711510104396639</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2886057295149593</v>
+        <v>0.2886640085641657</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3234204588701934</v>
+        <v>0.3225659418923026</v>
       </c>
       <c r="F190" t="n">
-        <v>0.08762645637990077</v>
+        <v>0.08773597187766925</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0394762106189735</v>
+        <v>0.03935428317172828</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0.05287647740839491</v>
+        <v>0.05326829222217941</v>
       </c>
       <c r="B191" t="n">
-        <v>0.03697297875677075</v>
+        <v>0.03736649336172429</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1710323937566071</v>
+        <v>0.1710454679670892</v>
       </c>
       <c r="D191" t="n">
-        <v>0.2890576920730851</v>
+        <v>0.2890943317055205</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3228026840070829</v>
+        <v>0.3219740186028007</v>
       </c>
       <c r="F191" t="n">
-        <v>0.08776484387056896</v>
+        <v>0.08787726830763168</v>
       </c>
       <c r="G191" t="n">
-        <v>0.03949293012749018</v>
+        <v>0.03937412783305433</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0.05296937404176785</v>
+        <v>0.05336190609685918</v>
       </c>
       <c r="B192" t="n">
-        <v>0.03698519836941788</v>
+        <v>0.03737697783605159</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1709340407625929</v>
+        <v>0.1709379705196013</v>
       </c>
       <c r="D192" t="n">
-        <v>0.2895535791696672</v>
+        <v>0.289565450303106</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3221467452127814</v>
+        <v>0.3213474548926719</v>
       </c>
       <c r="F192" t="n">
-        <v>0.08790179384775898</v>
+        <v>0.0880167539684345</v>
       </c>
       <c r="G192" t="n">
-        <v>0.03950926859601409</v>
+        <v>0.03939348638327522</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.05306133556339907</v>
+        <v>0.05345418048994467</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0369968999493864</v>
+        <v>0.03738692838818189</v>
       </c>
       <c r="C193" t="n">
-        <v>0.17083299963863</v>
+        <v>0.1708285426758543</v>
       </c>
       <c r="D193" t="n">
-        <v>0.290089149428044</v>
+        <v>0.2900737640730379</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3214566961535329</v>
+        <v>0.3206895428564481</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0880376504630202</v>
+        <v>0.08815465465730075</v>
       </c>
       <c r="G193" t="n">
-        <v>0.03952526880398779</v>
+        <v>0.0394123868592322</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.05315228443742959</v>
+        <v>0.05354510893680395</v>
       </c>
       <c r="B194" t="n">
-        <v>0.03700811264832257</v>
+        <v>0.0373963793932968</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1707291410380019</v>
+        <v>0.1707172266212886</v>
       </c>
       <c r="D194" t="n">
-        <v>0.2906588186179141</v>
+        <v>0.2906141679460373</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3207379181236859</v>
+        <v>0.3200050629865797</v>
       </c>
       <c r="F194" t="n">
-        <v>0.08817274960032621</v>
+        <v>0.08829119372884632</v>
       </c>
       <c r="G194" t="n">
-        <v>0.03954097553431968</v>
+        <v>0.0394308603871474</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.05324213784699789</v>
+        <v>0.0536346809646621</v>
       </c>
       <c r="B195" t="n">
-        <v>0.03701886029770941</v>
+        <v>0.03740536827058267</v>
       </c>
       <c r="C195" t="n">
-        <v>0.1706223697138518</v>
+        <v>0.170604078554271</v>
       </c>
       <c r="D195" t="n">
-        <v>0.2912557926001987</v>
+        <v>0.2911801974280517</v>
       </c>
       <c r="E195" t="n">
-        <v>0.3199969914050729</v>
+        <v>0.3193001449954134</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0883074133232289</v>
+        <v>0.08842658909437394</v>
       </c>
       <c r="G195" t="n">
-        <v>0.03955643481294082</v>
+        <v>0.03944894069264542</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.05333080999535144</v>
+        <v>0.05372288212711233</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0370291628710271</v>
+        <v>0.03741393581836829</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1705126233141352</v>
+        <v>0.1704891650604244</v>
       </c>
       <c r="D196" t="n">
-        <v>0.2918722447268224</v>
+        <v>0.2917642253064915</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3192415220590156</v>
+        <v>0.3185820781247249</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0884419440775786</v>
+        <v>0.08856105010670248</v>
       </c>
       <c r="G196" t="n">
-        <v>0.03957169295606969</v>
+        <v>0.03946666345617623</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0.05341821446979903</v>
+        <v>0.0538096941269986</v>
       </c>
       <c r="B197" t="n">
-        <v>0.03703903793830015</v>
+        <v>0.03742212589575065</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1703998711996743</v>
+        <v>0.1703725598349934</v>
       </c>
       <c r="D197" t="n">
-        <v>0.2924995309201184</v>
+        <v>0.2923577014283245</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3184799309995606</v>
+        <v>0.3178590788469601</v>
       </c>
       <c r="F197" t="n">
-        <v>0.08857661896126817</v>
+        <v>0.08869477433348269</v>
       </c>
       <c r="G197" t="n">
-        <v>0.03958679551127935</v>
+        <v>0.03948406553349031</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.05350426645037389</v>
+        <v>0.05389509503168608</v>
       </c>
       <c r="B198" t="n">
-        <v>0.03704850187013454</v>
+        <v>0.0374299844751745</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1702841139641482</v>
+        <v>0.1702543410598123</v>
       </c>
       <c r="D198" t="n">
-        <v>0.2931284345637602</v>
+        <v>0.29295142655434</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3177212130018663</v>
+        <v>0.3171400245482965</v>
       </c>
       <c r="F198" t="n">
-        <v>0.0887116841068168</v>
+        <v>0.08882794425781343</v>
       </c>
       <c r="G198" t="n">
-        <v>0.03960178604289991</v>
+        <v>0.03950118407287741</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0.05358888472852029</v>
+        <v>0.05397905958355415</v>
       </c>
       <c r="B199" t="n">
-        <v>0.03705757075244479</v>
+        <v>0.03743755815137627</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1701653832331911</v>
+        <v>0.1701345896313318</v>
       </c>
       <c r="D199" t="n">
-        <v>0.2937494326162078</v>
+        <v>0.2935358506287893</v>
       </c>
       <c r="E199" t="n">
-        <v>0.3169746743455407</v>
+        <v>0.3164341624424735</v>
       </c>
       <c r="F199" t="n">
-        <v>0.08884734941591836</v>
+        <v>0.0889607239910799</v>
       </c>
       <c r="G199" t="n">
-        <v>0.03961670490817671</v>
+        <v>0.03951805557139501</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.0536719934295246</v>
+        <v>0.05406155960906636</v>
       </c>
       <c r="B200" t="n">
-        <v>0.03706626086728063</v>
+        <v>0.03744489224538301</v>
       </c>
       <c r="C200" t="n">
-        <v>0.17004374155947</v>
+        <v>0.1700133883079188</v>
       </c>
       <c r="D200" t="n">
-        <v>0.2943529738727228</v>
+        <v>0.2941013851995832</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3162496583586976</v>
+        <v>0.3157508035877294</v>
       </c>
       <c r="F200" t="n">
-        <v>0.08898378388761867</v>
+        <v>0.08909325613049046</v>
       </c>
       <c r="G200" t="n">
-        <v>0.03963158802468574</v>
+        <v>0.03953471491982868</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0.05375352343242682</v>
+        <v>0.0541425645311577</v>
       </c>
       <c r="B201" t="n">
-        <v>0.03707458875772589</v>
+        <v>0.03745202868361691</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1699192825094415</v>
+        <v>0.1698908217170554</v>
       </c>
       <c r="D201" t="n">
-        <v>0.2949297594337311</v>
+        <v>0.2946387192314571</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3155552683131142</v>
+        <v>0.315099012417659</v>
       </c>
       <c r="F201" t="n">
-        <v>0.08912111176800989</v>
+        <v>0.08922565892861936</v>
       </c>
       <c r="G201" t="n">
-        <v>0.03964646578555049</v>
+        <v>0.03955119449043434</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0.0538334134340189</v>
+        <v>0.05422204199080095</v>
       </c>
       <c r="B202" t="n">
-        <v>0.03708257089355185</v>
+        <v>0.03745900385823689</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1697921300974797</v>
+        <v>0.1697669770523225</v>
       </c>
       <c r="D202" t="n">
-        <v>0.295471016444038</v>
+        <v>0.2951391272619343</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3149000972358532</v>
+        <v>0.314487302555347</v>
       </c>
       <c r="F202" t="n">
-        <v>0.08925940973510682</v>
+        <v>0.08935802395902227</v>
       </c>
       <c r="G202" t="n">
-        <v>0.03966136215995131</v>
+        <v>0.0395675233223364</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0.05391161071135415</v>
+        <v>0.05429995858226763</v>
       </c>
       <c r="B203" t="n">
-        <v>0.03709022302387508</v>
+        <v>0.03746584668215856</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1696624377844108</v>
+        <v>0.169641945208136</v>
       </c>
       <c r="D203" t="n">
-        <v>0.2959687557765799</v>
+        <v>0.2955947588628043</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3142919732367674</v>
+        <v>0.3139233497555391</v>
       </c>
       <c r="F203" t="n">
-        <v>0.0893987053735134</v>
+        <v>0.08949041445384248</v>
       </c>
       <c r="G203" t="n">
-        <v>0.03967629409349937</v>
+        <v>0.03958372645525216</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.05398807153546993</v>
+        <v>0.05437628070194021</v>
       </c>
       <c r="B204" t="n">
-        <v>0.03709755937321981</v>
+        <v>0.03747257703955771</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1695303865328039</v>
+        <v>0.1695158220538925</v>
       </c>
       <c r="D204" t="n">
-        <v>0.296416005842309</v>
+        <v>0.295998898769667</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3137377285377999</v>
+        <v>0.3134137325222803</v>
       </c>
       <c r="F204" t="n">
-        <v>0.08953897693182725</v>
+        <v>0.08962286445836441</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03969127124657039</v>
+        <v>0.0395998244542981</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.05406276140197526</v>
+        <v>0.05445097550210278</v>
       </c>
       <c r="B205" t="n">
-        <v>0.03710459178153987</v>
+        <v>0.0374792047992956</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1693961817003692</v>
+        <v>0.1693887095429455</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2968070149160125</v>
+        <v>0.2963461878871841</v>
       </c>
       <c r="E205" t="n">
-        <v>0.3132429993077647</v>
+        <v>0.3129637102142538</v>
       </c>
       <c r="F205" t="n">
-        <v>0.08968015474686114</v>
+        <v>0.0897553788967816</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03970629614547729</v>
+        <v>0.03961583315743678</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.05413565495693041</v>
+        <v>0.05452401193018223</v>
       </c>
       <c r="B206" t="n">
-        <v>0.03711132898489748</v>
+        <v>0.03748572950720862</v>
       </c>
       <c r="C206" t="n">
-        <v>0.1692600490858875</v>
+        <v>0.1692607163893741</v>
       </c>
       <c r="D206" t="n">
-        <v>0.2971374166974374</v>
+        <v>0.2966327966768411</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3128120616094607</v>
+        <v>0.3125770472555163</v>
       </c>
       <c r="F206" t="n">
-        <v>0.08982212396730541</v>
+        <v>0.08988793457761282</v>
       </c>
       <c r="G206" t="n">
-        <v>0.03972136469808094</v>
+        <v>0.03963176366326475</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.05420673588655356</v>
+        <v>0.05459536182099907</v>
       </c>
       <c r="B207" t="n">
-        <v>0.03711777612089725</v>
+        <v>0.03749214080756981</v>
       </c>
       <c r="C207" t="n">
-        <v>0.1691222299853203</v>
+        <v>0.1691319581233985</v>
       </c>
       <c r="D207" t="n">
-        <v>0.2974043536705792</v>
+        <v>0.2968565441600589</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3124477082328048</v>
+        <v>0.3122558904348718</v>
       </c>
       <c r="F207" t="n">
-        <v>0.08996472899005968</v>
+        <v>0.09002048209108093</v>
       </c>
       <c r="G207" t="n">
-        <v>0.03973646711378519</v>
+        <v>0.03964762256202089</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0.05427599658709879</v>
+        <v>0.05466500099905969</v>
       </c>
       <c r="B208" t="n">
-        <v>0.03712393457221758</v>
+        <v>0.03749841957241493</v>
       </c>
       <c r="C208" t="n">
-        <v>0.1689829754427997</v>
+        <v>0.1690025564533463</v>
       </c>
       <c r="D208" t="n">
-        <v>0.2976065553346924</v>
+        <v>0.2970169578493772</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3121511700395239</v>
+        <v>0.3120007042546807</v>
       </c>
       <c r="F208" t="n">
-        <v>0.09010777895884087</v>
+        <v>0.09015294847406724</v>
       </c>
       <c r="G208" t="n">
-        <v>0.03975158906482677</v>
+        <v>0.03966341239705426</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0.05434343793775842</v>
+        <v>0.05473291033999278</v>
       </c>
       <c r="B209" t="n">
-        <v>0.03712980219067293</v>
+        <v>0.0375045396470348</v>
       </c>
       <c r="C209" t="n">
-        <v>0.1688425406000704</v>
+        <v>0.1688726379980641</v>
       </c>
       <c r="D209" t="n">
-        <v>0.2977443675717388</v>
+        <v>0.2971152722630079</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3119220839506988</v>
+        <v>0.3118102669766837</v>
       </c>
       <c r="F209" t="n">
-        <v>0.09025105459042149</v>
+        <v>0.09028524044679778</v>
       </c>
       <c r="G209" t="n">
-        <v>0.03976671315863907</v>
+        <v>0.03967913232841934</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.05440906889582141</v>
+        <v>0.05479907673777616</v>
       </c>
       <c r="B210" t="n">
-        <v>0.03713537386195034</v>
+        <v>0.0375104700610074</v>
       </c>
       <c r="C210" t="n">
-        <v>0.1687011789937433</v>
+        <v>0.1687423325899357</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2978197323101883</v>
+        <v>0.29715436615949</v>
       </c>
       <c r="E210" t="n">
-        <v>0.311758510055449</v>
+        <v>0.3116817275232784</v>
       </c>
       <c r="F210" t="n">
-        <v>0.09039431546267251</v>
+        <v>0.09041724797347521</v>
       </c>
       <c r="G210" t="n">
-        <v>0.03978182042017485</v>
+        <v>0.03969477895503704</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0.05447290615899811</v>
+        <v>0.05486349392787669</v>
       </c>
       <c r="B211" t="n">
-        <v>0.03714064239002119</v>
+        <v>0.03751617751294004</v>
       </c>
       <c r="C211" t="n">
-        <v>0.1685591375502757</v>
+        <v>0.1686117714528262</v>
       </c>
       <c r="D211" t="n">
-        <v>0.2978361158953249</v>
+        <v>0.2971386411412218</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3116569984633617</v>
+        <v>0.3116107208525036</v>
       </c>
       <c r="F211" t="n">
-        <v>0.09053730772936149</v>
+        <v>0.09054884787463385</v>
       </c>
       <c r="G211" t="n">
-        <v>0.03979689181265676</v>
+        <v>0.03971034723799808</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>0.05453497381502512</v>
+        <v>0.05492616312491936</v>
       </c>
       <c r="B212" t="n">
-        <v>0.03714559957596015</v>
+        <v>0.03752162891876028</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1684166528326397</v>
+        <v>0.16848108560739</v>
       </c>
       <c r="D212" t="n">
-        <v>0.2977983867754845</v>
+        <v>0.2970738467004782</v>
       </c>
       <c r="E212" t="n">
-        <v>0.3116127055665611</v>
+        <v>0.3115915369625751</v>
       </c>
       <c r="F212" t="n">
-        <v>0.09067977180094895</v>
+        <v>0.09067990722925133</v>
       </c>
       <c r="G212" t="n">
-        <v>0.03981190963338038</v>
+        <v>0.03972583145662587</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>0.05459530289660394</v>
+        <v>0.05498709344566376</v>
       </c>
       <c r="B213" t="n">
-        <v>0.03715023737737772</v>
+        <v>0.03752679381860212</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1682739485124623</v>
+        <v>0.1683504048327853</v>
       </c>
       <c r="D213" t="n">
-        <v>0.2977126446923719</v>
+        <v>0.2969668590276842</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3116195583961544</v>
+        <v>0.3116173364040311</v>
       </c>
       <c r="F213" t="n">
-        <v>0.09082144946579696</v>
+        <v>0.09081028634886724</v>
       </c>
       <c r="G213" t="n">
-        <v>0.03982685865923307</v>
+        <v>0.03974122612236646</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0.05465393092855654</v>
+        <v>0.05504630210099895</v>
       </c>
       <c r="B214" t="n">
-        <v>0.0371545489989842</v>
+        <v>0.03753164646322243</v>
       </c>
       <c r="C214" t="n">
-        <v>0.1681312346543221</v>
+        <v>0.1682198574163887</v>
       </c>
       <c r="D214" t="n">
-        <v>0.2975860055651267</v>
+        <v>0.296825422884486</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3116704623989156</v>
+        <v>0.3116804031759741</v>
       </c>
       <c r="F214" t="n">
-        <v>0.09096209046931064</v>
+        <v>0.09093984118345332</v>
       </c>
       <c r="G214" t="n">
-        <v>0.03984172698478413</v>
+        <v>0.03975652677547625</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0.05471090138835567</v>
+        <v>0.05510381435256349</v>
       </c>
       <c r="B215" t="n">
-        <v>0.03715852984027851</v>
+        <v>0.03753616744247759</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1679887080542122</v>
+        <v>0.1680895707614625</v>
       </c>
       <c r="D215" t="n">
-        <v>0.2974263491614019</v>
+        <v>0.2966578674804294</v>
       </c>
       <c r="E215" t="n">
-        <v>0.3117575468589267</v>
+        <v>0.3117724242412921</v>
       </c>
       <c r="F215" t="n">
-        <v>0.09110145816775973</v>
+        <v>0.09106842512431518</v>
       </c>
       <c r="G215" t="n">
-        <v>0.03985650652906499</v>
+        <v>0.03977173059746005</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0.05476626302134505</v>
+        <v>0.05515966323810565</v>
       </c>
       <c r="B216" t="n">
-        <v>0.03716217818289177</v>
+        <v>0.0375403447686671</v>
       </c>
       <c r="C216" t="n">
-        <v>0.167846553747036</v>
+        <v>0.1679596727262293</v>
       </c>
       <c r="D216" t="n">
-        <v>0.2972420394875699</v>
+        <v>0.2964728084930841</v>
       </c>
       <c r="E216" t="n">
-        <v>0.3118724382324166</v>
+        <v>0.3118847836942893</v>
       </c>
       <c r="F216" t="n">
-        <v>0.09123933419236321</v>
+        <v>0.09119589029229694</v>
       </c>
       <c r="G216" t="n">
-        <v>0.03987119313637738</v>
+        <v>0.03978683678732778</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0.05482006899744599</v>
+        <v>0.05521388907655234</v>
       </c>
       <c r="B217" t="n">
-        <v>0.03716549556651905</v>
+        <v>0.03754417438041067</v>
       </c>
       <c r="C217" t="n">
-        <v>0.1677049470762098</v>
+        <v>0.1678302933741499</v>
       </c>
       <c r="D217" t="n">
-        <v>0.2970416297605969</v>
+        <v>0.2962788490328536</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3120065500759858</v>
+        <v>0.3120088589449909</v>
       </c>
       <c r="F217" t="n">
-        <v>0.09137552218772138</v>
+        <v>0.09132208851909202</v>
       </c>
       <c r="G217" t="n">
-        <v>0.03988578633552146</v>
+        <v>0.03980184667195067</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0.05487237604379866</v>
+        <v>0.05526653876849209</v>
       </c>
       <c r="B218" t="n">
-        <v>0.03716848682231719</v>
+        <v>0.03754766008247204</v>
       </c>
       <c r="C218" t="n">
-        <v>0.1675640557986287</v>
+        <v>0.1677015666753884</v>
       </c>
       <c r="D218" t="n">
-        <v>0.296833565682681</v>
+        <v>0.296084292373054</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3121513758824006</v>
+        <v>0.3121363062400053</v>
       </c>
       <c r="F218" t="n">
-        <v>0.09150985094477833</v>
+        <v>0.09144687231413706</v>
       </c>
       <c r="G218" t="n">
-        <v>0.03990028882539535</v>
+        <v>0.03981676354645141</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0.05492324334663443</v>
+        <v>0.05531766491379574</v>
       </c>
       <c r="B219" t="n">
-        <v>0.03717115982465917</v>
+        <v>0.03755081297943502</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1674240416170133</v>
+        <v>0.1675736316503475</v>
       </c>
       <c r="D219" t="n">
-        <v>0.2966259021073995</v>
+        <v>0.2958968785575919</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3122987708047482</v>
+        <v>0.3122593234971879</v>
       </c>
       <c r="F219" t="n">
-        <v>0.09164217659607035</v>
+        <v>0.09157009613392754</v>
       </c>
       <c r="G219" t="n">
-        <v>0.03991470570347486</v>
+        <v>0.03983159226771427</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0.05497273136678046</v>
+        <v>0.0553673247750475</v>
       </c>
       <c r="B220" t="n">
-        <v>0.03717352496092711</v>
+        <v>0.03755365049369558</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1672850607769413</v>
+        <v>0.1674466325072697</v>
       </c>
       <c r="D220" t="n">
-        <v>0.2964260463982204</v>
+        <v>0.2957235555318271</v>
       </c>
       <c r="E220" t="n">
-        <v>0.3124412086262015</v>
+        <v>0.3123708798228589</v>
       </c>
       <c r="F220" t="n">
-        <v>0.09177238432493405</v>
+        <v>0.09169161822039158</v>
       </c>
       <c r="G220" t="n">
-        <v>0.03992904354599543</v>
+        <v>0.03984633864890978</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0.0550209005448349</v>
+        <v>0.05541557912303784</v>
       </c>
       <c r="B221" t="n">
-        <v>0.03717559444831426</v>
+        <v>0.03755619507911663</v>
       </c>
       <c r="C221" t="n">
-        <v>0.1671472635440303</v>
+        <v>0.1673207174797482</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2962405406722224</v>
+        <v>0.2955702932765279</v>
       </c>
       <c r="E221" t="n">
-        <v>0.3125720019047208</v>
+        <v>0.3124649031583247</v>
       </c>
       <c r="F221" t="n">
-        <v>0.09190038945128709</v>
+        <v>0.09181130316056381</v>
       </c>
       <c r="G221" t="n">
-        <v>0.03994330943459026</v>
+        <v>0.03986100872268113</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0.05506781010131472</v>
+        <v>0.05546249100807288</v>
       </c>
       <c r="B222" t="n">
-        <v>0.0371773815461013</v>
+        <v>0.03755847275072742</v>
       </c>
       <c r="C222" t="n">
-        <v>0.1670107926283275</v>
+        <v>0.1671960362853563</v>
       </c>
       <c r="D222" t="n">
-        <v>0.296074891343771</v>
+        <v>0.2954419467052997</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3126854759483436</v>
+        <v>0.3125364201267796</v>
       </c>
       <c r="F222" t="n">
-        <v>0.09202613838389311</v>
+        <v>0.09192902517026963</v>
       </c>
       <c r="G222" t="n">
-        <v>0.03995751004824889</v>
+        <v>0.03987560795349494</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0.05511351677072911</v>
+        <v>0.05550812450554044</v>
       </c>
       <c r="B223" t="n">
-        <v>0.03717889979348153</v>
+        <v>0.03756051154844309</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1668757803001362</v>
+        <v>0.1670727363494174</v>
       </c>
       <c r="D223" t="n">
-        <v>0.2959334519829069</v>
+        <v>0.295342170063131</v>
       </c>
       <c r="E223" t="n">
-        <v>0.3127770913347529</v>
+        <v>0.3125816450978723</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0921496089814736</v>
+        <v>0.09204467195192065</v>
       </c>
       <c r="G223" t="n">
-        <v>0.03997165083651973</v>
+        <v>0.03989014048367525</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0.05515807364316868</v>
+        <v>0.05555254348571829</v>
       </c>
       <c r="B224" t="n">
-        <v>0.03718016230234222</v>
+        <v>0.0375623400411505</v>
       </c>
       <c r="C224" t="n">
-        <v>0.1667423449019897</v>
+        <v>0.1669509581296334</v>
       </c>
       <c r="D224" t="n">
-        <v>0.2958193606572661</v>
+        <v>0.2952733825286682</v>
       </c>
       <c r="E224" t="n">
-        <v>0.3128435124244272</v>
+        <v>0.3125980184679051</v>
       </c>
       <c r="F224" t="n">
-        <v>0.09227081070754364</v>
+        <v>0.09215814885401752</v>
       </c>
       <c r="G224" t="n">
-        <v>0.0399857353632627</v>
+        <v>0.03990460849290711</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.05520152916559396</v>
+        <v>0.05559581045530373</v>
       </c>
       <c r="B225" t="n">
-        <v>0.03718118122225041</v>
+        <v>0.03756398595861304</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1666105870729033</v>
+        <v>0.1668308300061811</v>
       </c>
       <c r="D225" t="n">
-        <v>0.2957345300574314</v>
+        <v>0.2952367819757134</v>
       </c>
       <c r="E225" t="n">
-        <v>0.3128826232469238</v>
+        <v>0.3125841968802516</v>
       </c>
       <c r="F225" t="n">
-        <v>0.09238978435583245</v>
+        <v>0.092269382985723</v>
       </c>
       <c r="G225" t="n">
-        <v>0.03999976487906461</v>
+        <v>0.03991901173821391</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0.05524392633531725</v>
+        <v>0.05563798551158961</v>
       </c>
       <c r="B226" t="n">
-        <v>0.03718196739142254</v>
+        <v>0.03756547501598585</v>
       </c>
       <c r="C226" t="n">
-        <v>0.1664805858163435</v>
+        <v>0.1667124632506392</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2956796859041633</v>
+        <v>0.2952324016360466</v>
       </c>
       <c r="E226" t="n">
-        <v>0.3128934950572949</v>
+        <v>0.3125400003393825</v>
       </c>
       <c r="F226" t="n">
-        <v>0.09250660136439835</v>
+        <v>0.09237832692434686</v>
       </c>
       <c r="G226" t="n">
-        <v>0.04001373813106052</v>
+        <v>0.03993334732200947</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0.05528530211764638</v>
+        <v>0.05567912544177958</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0371825301728988</v>
+        <v>0.03756682997249668</v>
       </c>
       <c r="C227" t="n">
-        <v>0.1663523951898648</v>
+        <v>0.1665959475577955</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2956544467424509</v>
+        <v>0.2952592028764043</v>
       </c>
       <c r="E227" t="n">
-        <v>0.3128763117534456</v>
+        <v>0.3124663227436179</v>
       </c>
       <c r="F227" t="n">
-        <v>0.09262136262748674</v>
+        <v>0.09248496169538416</v>
       </c>
       <c r="G227" t="n">
-        <v>0.04002765139620689</v>
+        <v>0.03994760971252238</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.05532568706966298</v>
+        <v>0.05571928298892471</v>
       </c>
       <c r="B228" t="n">
-        <v>0.03718287754397254</v>
+        <v>0.03756806994423945</v>
       </c>
       <c r="C228" t="n">
-        <v>0.166226041965336</v>
+        <v>0.16648134752869</v>
       </c>
       <c r="D228" t="n">
-        <v>0.2956574376312632</v>
+        <v>0.2953151965003514</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3128322606158679</v>
+        <v>0.3123650132325289</v>
       </c>
       <c r="F228" t="n">
-        <v>0.09273419640834211</v>
+        <v>0.09258929878977151</v>
       </c>
       <c r="G228" t="n">
-        <v>0.04004149876555553</v>
+        <v>0.03996179101549426</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>0.05536510533191497</v>
+        <v>0.05575850629587566</v>
       </c>
       <c r="B229" t="n">
-        <v>0.03718301631265643</v>
+        <v>0.03756920997372626</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1661015248921669</v>
+        <v>0.1663687003574645</v>
       </c>
       <c r="D229" t="n">
-        <v>0.2956864287366609</v>
+        <v>0.2953975848450837</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3127633963419266</v>
+        <v>0.3122387359634582</v>
       </c>
       <c r="F229" t="n">
-        <v>0.09284525574655059</v>
+        <v>0.09269138109263989</v>
       </c>
       <c r="G229" t="n">
-        <v>0.04005527263812361</v>
+        <v>0.03997588147175186</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0.05540357476796797</v>
+        <v>0.05579683852913411</v>
       </c>
       <c r="B230" t="n">
-        <v>0.0371829525071326</v>
+        <v>0.0375702608465189</v>
       </c>
       <c r="C230" t="n">
-        <v>0.1659788148400489</v>
+        <v>0.1662580148267925</v>
       </c>
       <c r="D230" t="n">
-        <v>0.2957384918570211</v>
+        <v>0.2955029173227527</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3126724870842678</v>
+        <v>0.3120908156368954</v>
       </c>
       <c r="F230" t="n">
-        <v>0.09295471461707167</v>
+        <v>0.0927912827040642</v>
       </c>
       <c r="G230" t="n">
-        <v>0.04006896432649017</v>
+        <v>0.03998987013384218</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0.05544110743443924</v>
+        <v>0.05583431767696367</v>
       </c>
       <c r="B231" t="n">
-        <v>0.03718269185117841</v>
+        <v>0.03757122913749327</v>
       </c>
       <c r="C231" t="n">
-        <v>0.1658578572605631</v>
+        <v>0.1661492715844859</v>
       </c>
       <c r="D231" t="n">
-        <v>0.2958101661957468</v>
+        <v>0.2956272527768531</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3125628491718965</v>
+        <v>0.3119250754491265</v>
       </c>
       <c r="F231" t="n">
-        <v>0.09306276328536763</v>
+        <v>0.09288910771653901</v>
       </c>
       <c r="G231" t="n">
-        <v>0.04008256480080855</v>
+        <v>0.04000374565853852</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>0.05547771025485554</v>
+        <v>0.05587097651055838</v>
       </c>
       <c r="B232" t="n">
-        <v>0.03718224029745332</v>
+        <v>0.03757211746562772</v>
       </c>
       <c r="C232" t="n">
-        <v>0.1657385758493871</v>
+        <v>0.1660424245680775</v>
       </c>
       <c r="D232" t="n">
-        <v>0.2958976273271847</v>
+        <v>0.2957663229043217</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3124381782437408</v>
+        <v>0.3117456733410902</v>
       </c>
       <c r="F232" t="n">
-        <v>0.09316960257492551</v>
+        <v>0.09298498806868233</v>
       </c>
       <c r="G232" t="n">
-        <v>0.04009606545245304</v>
+        <v>0.04001749714164218</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0.05551338591430729</v>
+        <v>0.05590684269252698</v>
       </c>
       <c r="B233" t="n">
-        <v>0.03718160458633517</v>
+        <v>0.03757292493377349</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1656208776077724</v>
+        <v>0.1659374033716111</v>
       </c>
       <c r="D233" t="n">
-        <v>0.2959968530045017</v>
+        <v>0.2959156918904411</v>
       </c>
       <c r="E233" t="n">
-        <v>0.31230238266458</v>
+        <v>0.311556941572061</v>
       </c>
       <c r="F233" t="n">
-        <v>0.09327543737324354</v>
+        <v>0.09307908062130935</v>
       </c>
       <c r="G233" t="n">
-        <v>0.04010945884926024</v>
+        <v>0.04003111491827713</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0.05554813391106758</v>
+        <v>0.05594193901392006</v>
       </c>
       <c r="B234" t="n">
-        <v>0.03718079273034516</v>
+        <v>0.03757364772808924</v>
       </c>
       <c r="C234" t="n">
-        <v>0.1655046594296642</v>
+        <v>0.1658341163057848</v>
       </c>
       <c r="D234" t="n">
-        <v>0.2961037805768573</v>
+        <v>0.2960709082251382</v>
       </c>
       <c r="E234" t="n">
-        <v>0.3121594243625952</v>
+        <v>0.3113632338634435</v>
       </c>
       <c r="F234" t="n">
-        <v>0.09338046961665582</v>
+        <v>0.09317156360822569</v>
       </c>
       <c r="G234" t="n">
-        <v>0.04012273937281496</v>
+        <v>0.04004459125539838</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0.05558195165720547</v>
+        <v>0.05597628373815808</v>
       </c>
       <c r="B235" t="n">
-        <v>0.03717981447375431</v>
+        <v>0.03757427984784902</v>
       </c>
       <c r="C235" t="n">
-        <v>0.1653898146958422</v>
+        <v>0.1657324538859349</v>
       </c>
       <c r="D235" t="n">
-        <v>0.2962144519749096</v>
+        <v>0.2962276453723003</v>
       </c>
       <c r="E235" t="n">
-        <v>0.3120131725087848</v>
+        <v>0.3111687836741067</v>
       </c>
       <c r="F235" t="n">
-        <v>0.09348489099346742</v>
+        <v>0.09326263260836591</v>
       </c>
       <c r="G235" t="n">
-        <v>0.04013590369603585</v>
+        <v>0.04005792087328541</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0.0556148356361469</v>
+        <v>0.05600989102860003</v>
       </c>
       <c r="B236" t="n">
-        <v>0.03717868162763312</v>
+        <v>0.03757481393111611</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1652762402335962</v>
+        <v>0.1656322924886357</v>
       </c>
       <c r="D236" t="n">
-        <v>0.2963251422950012</v>
+        <v>0.2963818285501377</v>
       </c>
       <c r="E236" t="n">
-        <v>0.3118672730790031</v>
+        <v>0.3109775765781335</v>
       </c>
       <c r="F236" t="n">
-        <v>0.09358887607891025</v>
+        <v>0.0933524961749905</v>
       </c>
       <c r="G236" t="n">
-        <v>0.04014895104970916</v>
+        <v>0.04007110124838621</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>0.05564678246456206</v>
+        <v>0.05604277143512144</v>
       </c>
       <c r="B237" t="n">
-        <v>0.03717740825734576</v>
+        <v>0.03757524213452864</v>
       </c>
       <c r="C237" t="n">
-        <v>0.1651638420403913</v>
+        <v>0.1655334979431972</v>
       </c>
       <c r="D237" t="n">
-        <v>0.2964324694344472</v>
+        <v>0.2965297453717459</v>
       </c>
       <c r="E237" t="n">
-        <v>0.3117250383845279</v>
+        <v>0.310793239199346</v>
       </c>
       <c r="F237" t="n">
-        <v>0.09369257621855487</v>
+        <v>0.09344137124670554</v>
       </c>
       <c r="G237" t="n">
-        <v>0.04016188320017081</v>
+        <v>0.040084132669355</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0.05567778993173195</v>
+        <v>0.05607493241443515</v>
       </c>
       <c r="B238" t="n">
-        <v>0.03717601074538335</v>
+        <v>0.03757555701833373</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1650525404672375</v>
+        <v>0.1654359288658805</v>
       </c>
       <c r="D238" t="n">
-        <v>0.2965334824575804</v>
+        <v>0.2966681385252225</v>
       </c>
       <c r="E238" t="n">
-        <v>0.3115893573956184</v>
+        <v>0.3106189466813916</v>
       </c>
       <c r="F238" t="n">
-        <v>0.09379611479023453</v>
+        <v>0.09352947845497672</v>
       </c>
       <c r="G238" t="n">
-        <v>0.04017470421221371</v>
+        <v>0.04009701803975983</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0.05570785784650632</v>
+        <v>0.05610637885964805</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0371745076700926</v>
+        <v>0.03757575238271797</v>
       </c>
       <c r="C239" t="n">
-        <v>0.1649422732471209</v>
+        <v>0.1653394396001406</v>
       </c>
       <c r="D239" t="n">
-        <v>0.2966257280702591</v>
+        <v>0.2967942790771875</v>
       </c>
       <c r="E239" t="n">
-        <v>0.3114626292081207</v>
+        <v>0.3104573502014362</v>
       </c>
       <c r="F239" t="n">
-        <v>0.09389958403931828</v>
+        <v>0.09361703743589721</v>
       </c>
       <c r="G239" t="n">
-        <v>0.04018741991858196</v>
+        <v>0.04010976244297264</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.05573698870521231</v>
+        <v>0.05613711361586207</v>
       </c>
       <c r="B240" t="n">
-        <v>0.03717291951035344</v>
+        <v>0.03757582399995493</v>
       </c>
       <c r="C240" t="n">
-        <v>0.164832996866911</v>
+        <v>0.1652438826878904</v>
       </c>
       <c r="D240" t="n">
-        <v>0.2967072947110288</v>
+        <v>0.296906019397555</v>
       </c>
       <c r="E240" t="n">
-        <v>0.3113467193939778</v>
+        <v>0.3103105255472259</v>
       </c>
       <c r="F240" t="n">
-        <v>0.09400304364452979</v>
+        <v>0.09370426224628475</v>
       </c>
       <c r="G240" t="n">
-        <v>0.04020003716798699</v>
+        <v>0.04012237250522737</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0.0557651880737143</v>
+        <v>0.05616713796169312</v>
       </c>
       <c r="B241" t="n">
-        <v>0.03717126818667994</v>
+        <v>0.03757577019102629</v>
       </c>
       <c r="C241" t="n">
-        <v>0.1647246858379031</v>
+        <v>0.1651491108649483</v>
       </c>
       <c r="D241" t="n">
-        <v>0.2967768354504883</v>
+        <v>0.2970018251527587</v>
       </c>
       <c r="E241" t="n">
-        <v>0.311242938711822</v>
+        <v>0.3101799432437101</v>
       </c>
       <c r="F241" t="n">
-        <v>0.09410652087114081</v>
+        <v>0.09379135697590876</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0402125628682516</v>
+        <v>0.04013485560995472</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.05579246494694572</v>
+        <v>0.05619645204075809</v>
       </c>
       <c r="B242" t="n">
-        <v>0.03716957647251588</v>
+        <v>0.0375755922051495</v>
       </c>
       <c r="C242" t="n">
-        <v>0.164617330777935</v>
+        <v>0.1650549786364135</v>
       </c>
       <c r="D242" t="n">
-        <v>0.2968335700688295</v>
+        <v>0.2970807863162429</v>
       </c>
       <c r="E242" t="n">
-        <v>0.3111520421129362</v>
+        <v>0.3100664601333965</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0942100125950682</v>
+        <v>0.0938785116386231</v>
       </c>
       <c r="G242" t="n">
-        <v>0.04022500302576938</v>
+        <v>0.04014721902941644</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.05581883174994762</v>
+        <v>0.0562250552323624</v>
       </c>
       <c r="B243" t="n">
-        <v>0.03716786730207574</v>
+        <v>0.03757529437622514</v>
       </c>
       <c r="C243" t="n">
-        <v>0.1645109347517474</v>
+        <v>0.1649613435395807</v>
       </c>
       <c r="D243" t="n">
-        <v>0.2968772696123634</v>
+        <v>0.2971426077067038</v>
       </c>
       <c r="E243" t="n">
-        <v>0.3110742466301751</v>
+        <v>0.3099703316851953</v>
       </c>
       <c r="F243" t="n">
-        <v>0.09431348824663337</v>
+        <v>0.09396589841308493</v>
       </c>
       <c r="G243" t="n">
-        <v>0.04023736170705761</v>
+        <v>0.04015946904684762</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0.05584430426334975</v>
+        <v>0.05625294645647324</v>
       </c>
       <c r="B244" t="n">
-        <v>0.03716616303373235</v>
+        <v>0.03757488404918731</v>
       </c>
       <c r="C244" t="n">
-        <v>0.1644055092477268</v>
+        <v>0.1648680672390378</v>
       </c>
       <c r="D244" t="n">
-        <v>0.2969082248704144</v>
+        <v>0.2971875801771234</v>
       </c>
       <c r="E244" t="n">
-        <v>0.3110092646717514</v>
+        <v>0.3098912436416923</v>
       </c>
       <c r="F244" t="n">
-        <v>0.09441689376828219</v>
+        <v>0.09405366829310452</v>
       </c>
       <c r="G244" t="n">
-        <v>0.04024964014474329</v>
+        <v>0.04017161014338145</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.0558689013777111</v>
+        <v>0.05628012441389017</v>
       </c>
       <c r="B245" t="n">
-        <v>0.0371644847369307</v>
+        <v>0.03757437128983156</v>
       </c>
       <c r="C245" t="n">
-        <v>0.1643010695428552</v>
+        <v>0.1647750166124981</v>
       </c>
       <c r="D245" t="n">
-        <v>0.2969272018335707</v>
+        <v>0.2972165342191444</v>
       </c>
       <c r="E245" t="n">
-        <v>0.3109563504960992</v>
+        <v>0.3098283609473405</v>
       </c>
       <c r="F245" t="n">
-        <v>0.09452015599070276</v>
+        <v>0.09414194819787082</v>
       </c>
       <c r="G245" t="n">
-        <v>0.04026183602213028</v>
+        <v>0.04018364431942447</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>0.05589264474178772</v>
+        <v>0.05630658776784199</v>
       </c>
       <c r="B246" t="n">
-        <v>0.03716285152810812</v>
+        <v>0.03757376841094349</v>
       </c>
       <c r="C246" t="n">
-        <v>0.1641976304770573</v>
+        <v>0.1646820649783008</v>
       </c>
       <c r="D246" t="n">
-        <v>0.2969353865510328</v>
+        <v>0.2972307783823269</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3109143566110881</v>
+        <v>0.3097803912654323</v>
       </c>
       <c r="F246" t="n">
-        <v>0.09462318708130074</v>
+        <v>0.09423083858578263</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0402739430096249</v>
+        <v>0.04019557060937157</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>0.05591555833863614</v>
+        <v>0.05633233527703358</v>
       </c>
       <c r="B247" t="n">
-        <v>0.03716128003844787</v>
+        <v>0.03757308936258503</v>
       </c>
       <c r="C247" t="n">
-        <v>0.1640952028962947</v>
+        <v>0.1645890935842714</v>
       </c>
       <c r="D247" t="n">
-        <v>0.2969343219541876</v>
+        <v>0.29723202548867</v>
       </c>
       <c r="E247" t="n">
-        <v>0.3108817974318325</v>
+        <v>0.3097456598412113</v>
       </c>
       <c r="F247" t="n">
-        <v>0.09472588871158902</v>
+        <v>0.09432041161308131</v>
       </c>
       <c r="G247" t="n">
-        <v>0.0402859506290122</v>
+        <v>0.04020738483314723</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0.05593766804545317</v>
+        <v>0.05635736589238804</v>
       </c>
       <c r="B248" t="n">
-        <v>0.03715978404926414</v>
+        <v>0.0375723490438083</v>
       </c>
       <c r="C248" t="n">
-        <v>0.1639937911106167</v>
+        <v>0.1644959934294604</v>
       </c>
       <c r="D248" t="n">
-        <v>0.2969258390555887</v>
+        <v>0.2972223100881943</v>
       </c>
       <c r="E248" t="n">
-        <v>0.3108569175334757</v>
+        <v>0.3097221920596831</v>
       </c>
       <c r="F248" t="n">
-        <v>0.09482815573521146</v>
+        <v>0.09441070987762321</v>
       </c>
       <c r="G248" t="n">
-        <v>0.0402978444703901</v>
+        <v>0.04021907960884268</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.05595900117732886</v>
+        <v>0.05638167883007873</v>
       </c>
       <c r="B249" t="n">
-        <v>0.03715837428777054</v>
+        <v>0.03757156259544694</v>
       </c>
       <c r="C249" t="n">
-        <v>0.1638933917148921</v>
+        <v>0.164402667430999</v>
       </c>
       <c r="D249" t="n">
-        <v>0.2969119845643653</v>
+        <v>0.2972039008973412</v>
       </c>
       <c r="E249" t="n">
-        <v>0.3108377623322886</v>
+        <v>0.3097077998287482</v>
       </c>
       <c r="F249" t="n">
-        <v>0.09492987918839427</v>
+        <v>0.0945017457877808</v>
       </c>
       <c r="G249" t="n">
-        <v>0.04030960673496022</v>
+        <v>0.04023064462960534</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>0.05597958602305114</v>
+        <v>0.0564052736315649</v>
       </c>
       <c r="B250" t="n">
-        <v>0.03715705841016862</v>
+        <v>0.03757074472951253</v>
       </c>
       <c r="C250" t="n">
-        <v>0.1637939937747371</v>
+        <v>0.1643090328856736</v>
       </c>
       <c r="D250" t="n">
-        <v>0.2968949470697793</v>
+        <v>0.2971792120408801</v>
       </c>
       <c r="E250" t="n">
-        <v>0.3108222491897923</v>
+        <v>0.3097001679354845</v>
       </c>
       <c r="F250" t="n">
-        <v>0.09503094845021061</v>
+        <v>0.09459350159046091</v>
       </c>
       <c r="G250" t="n">
-        <v>0.04032121708226063</v>
+        <v>0.04024206718642322</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>0.05642815021845108</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.0375699091406303</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.1642150241211785</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.2971507167527643</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.3096969367883772</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.09468593008013507</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.04025333289846375</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>0.05645030894587928</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.03756906803148233</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.1641205951892086</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.2971208667961546</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.3096957784524755</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.09477895598865198</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.04026442659614769</v>
       </c>
     </row>
   </sheetData>
